--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
   <si>
     <t>ECX</t>
   </si>
@@ -656,43 +656,43 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:L102"/>
+  <dimension ref="A5:M102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H7" s="2" t="s">
         <v>3</v>
       </c>
@@ -705,23 +705,26 @@
       <c r="K7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L7" s="2"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>491200</v>
+        <v>648700</v>
       </c>
       <c r="E8" s="3">
-        <v>383700</v>
+        <v>494500</v>
       </c>
       <c r="F8" s="3">
-        <v>309400</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>3</v>
+        <v>386300</v>
+      </c>
+      <c r="G8" s="3">
+        <v>311600</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -732,26 +735,29 @@
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K8" s="3">
-        <v>0</v>
-      </c>
-      <c r="L8" s="3"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="3">
+        <v>0</v>
+      </c>
+      <c r="M8" s="3"/>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>354400</v>
+        <v>472100</v>
       </c>
       <c r="E9" s="3">
-        <v>270900</v>
+        <v>356800</v>
       </c>
       <c r="F9" s="3">
-        <v>233300</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>3</v>
+        <v>272700</v>
+      </c>
+      <c r="G9" s="3">
+        <v>234900</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -765,23 +771,26 @@
       <c r="K9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L9" s="3"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M9" s="3"/>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>136800</v>
+        <v>176500</v>
       </c>
       <c r="E10" s="3">
-        <v>112800</v>
+        <v>137700</v>
       </c>
       <c r="F10" s="3">
-        <v>76100</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>3</v>
+        <v>113600</v>
+      </c>
+      <c r="G10" s="3">
+        <v>76700</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -795,9 +804,12 @@
       <c r="K10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L10" s="3"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M10" s="3"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -810,22 +822,23 @@
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="M11" s="3"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>163200</v>
+        <v>175800</v>
       </c>
       <c r="E12" s="3">
-        <v>162900</v>
+        <v>164400</v>
       </c>
       <c r="F12" s="3">
-        <v>93300</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>3</v>
+        <v>164000</v>
+      </c>
+      <c r="G12" s="3">
+        <v>94000</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -839,9 +852,12 @@
       <c r="K12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L12" s="3"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M12" s="3"/>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -869,23 +885,26 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
+      <c r="M13" s="3"/>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-9900</v>
+        <v>0</v>
       </c>
       <c r="E14" s="3">
+        <v>-10000</v>
+      </c>
+      <c r="F14" s="3">
         <v>-1500</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -896,27 +915,30 @@
       <c r="J14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3"/>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>9200</v>
+      <c r="D15" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E15" s="3">
+        <v>9300</v>
+      </c>
+      <c r="F15" s="3">
         <v>8800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>7900</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
       </c>
@@ -926,12 +948,15 @@
       <c r="J15" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
-      <c r="L15" s="3"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="K15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3"/>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -941,22 +966,23 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
-    </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M16" s="3"/>
+    </row>
+    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>683700</v>
+      <c r="D17" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E17" s="3">
-        <v>517800</v>
+        <v>688400</v>
       </c>
       <c r="F17" s="3">
-        <v>368900</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>3</v>
+        <v>521300</v>
+      </c>
+      <c r="G17" s="3">
+        <v>371400</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -970,23 +996,26 @@
       <c r="K17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L17" s="3"/>
-    </row>
-    <row r="18" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M17" s="3"/>
+    </row>
+    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>-192500</v>
+      <c r="D18" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E18" s="3">
-        <v>-134100</v>
+        <v>-193800</v>
       </c>
       <c r="F18" s="3">
-        <v>-59400</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>3</v>
+        <v>-135000</v>
+      </c>
+      <c r="G18" s="3">
+        <v>-59800</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1000,9 +1029,12 @@
       <c r="K18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L18" s="3"/>
-    </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M18" s="3"/>
+    </row>
+    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1015,23 +1047,24 @@
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
-    </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M19" s="3"/>
+    </row>
+    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-10200</v>
+      <c r="D20" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E20" s="3">
-        <v>-10900</v>
+        <v>-10300</v>
       </c>
       <c r="F20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="G20" s="3">
         <v>6900</v>
       </c>
-      <c r="G20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1044,23 +1077,26 @@
       <c r="K20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L20" s="3"/>
-    </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M20" s="3"/>
+    </row>
+    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>-193400</v>
+      <c r="D21" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E21" s="3">
-        <v>-136100</v>
+        <v>-194700</v>
       </c>
       <c r="F21" s="3">
-        <v>-44400</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>3</v>
+        <v>-137000</v>
+      </c>
+      <c r="G21" s="3">
+        <v>-44700</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1071,27 +1107,30 @@
       <c r="J21" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K21" s="3">
-        <v>0</v>
-      </c>
-      <c r="L21" s="3"/>
-    </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3"/>
+    </row>
+    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E22" s="3">
         <v>7100</v>
       </c>
-      <c r="E22" s="3">
-        <v>18200</v>
-      </c>
       <c r="F22" s="3">
+        <v>18300</v>
+      </c>
+      <c r="G22" s="3">
         <v>8200</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1101,26 +1140,29 @@
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3"/>
-    </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L22" s="3">
+        <v>0</v>
+      </c>
+      <c r="M22" s="3"/>
+    </row>
+    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-209800</v>
+        <v>-141600</v>
       </c>
       <c r="E23" s="3">
-        <v>-163200</v>
+        <v>-211300</v>
       </c>
       <c r="F23" s="3">
-        <v>-60700</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>3</v>
+        <v>-164300</v>
+      </c>
+      <c r="G23" s="3">
+        <v>-61100</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1134,23 +1176,26 @@
       <c r="K23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L23" s="3"/>
-    </row>
-    <row r="24" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M23" s="3"/>
+    </row>
+    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E24" s="3">
         <v>3000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>500</v>
       </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>3</v>
+      <c r="G24" s="3">
+        <v>0</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>3</v>
@@ -1161,12 +1206,15 @@
       <c r="J24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
-      <c r="L24" s="3"/>
-    </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3"/>
+    </row>
+    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1194,23 +1242,26 @@
       <c r="K25" s="3">
         <v>0</v>
       </c>
-      <c r="L25" s="3"/>
-    </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L25" s="3">
+        <v>0</v>
+      </c>
+      <c r="M25" s="3"/>
+    </row>
+    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>-212800</v>
+      <c r="D26" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E26" s="3">
-        <v>-163700</v>
+        <v>-214300</v>
       </c>
       <c r="F26" s="3">
-        <v>-60800</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>3</v>
+        <v>-164800</v>
+      </c>
+      <c r="G26" s="3">
+        <v>-61200</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1224,23 +1275,26 @@
       <c r="K26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L26" s="3"/>
-    </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M26" s="3"/>
+    </row>
+    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>-261600</v>
+      <c r="D27" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E27" s="3">
-        <v>-196700</v>
+        <v>-263400</v>
       </c>
       <c r="F27" s="3">
-        <v>-74700</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>3</v>
+        <v>-198000</v>
+      </c>
+      <c r="G27" s="3">
+        <v>-75200</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1254,9 +1308,12 @@
       <c r="K27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="3"/>
-    </row>
-    <row r="28" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="3"/>
+    </row>
+    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1284,9 +1341,12 @@
       <c r="K28" s="3">
         <v>0</v>
       </c>
-      <c r="L28" s="3"/>
-    </row>
-    <row r="29" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L28" s="3">
+        <v>0</v>
+      </c>
+      <c r="M28" s="3"/>
+    </row>
+    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1314,9 +1374,12 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3"/>
-    </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3"/>
+    </row>
+    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1344,9 +1407,12 @@
       <c r="K30" s="3">
         <v>0</v>
       </c>
-      <c r="L30" s="3"/>
-    </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3"/>
+    </row>
+    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1374,24 +1440,27 @@
       <c r="K31" s="3">
         <v>0</v>
       </c>
-      <c r="L31" s="3"/>
-    </row>
-    <row r="32" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L31" s="3">
+        <v>0</v>
+      </c>
+      <c r="M31" s="3"/>
+    </row>
+    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>10200</v>
+      <c r="D32" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E32" s="3">
-        <v>10900</v>
+        <v>10300</v>
       </c>
       <c r="F32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-6900</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1404,23 +1473,26 @@
       <c r="K32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L32" s="3"/>
-    </row>
-    <row r="33" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M32" s="3"/>
+    </row>
+    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>-261600</v>
+      <c r="D33" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E33" s="3">
-        <v>-196700</v>
+        <v>-263400</v>
       </c>
       <c r="F33" s="3">
-        <v>-74700</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>3</v>
+        <v>-198000</v>
+      </c>
+      <c r="G33" s="3">
+        <v>-75200</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1434,9 +1506,12 @@
       <c r="K33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L33" s="3"/>
-    </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M33" s="3"/>
+    </row>
+    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1464,23 +1539,26 @@
       <c r="K34" s="3">
         <v>0</v>
       </c>
-      <c r="L34" s="3"/>
-    </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L34" s="3">
+        <v>0</v>
+      </c>
+      <c r="M34" s="3"/>
+    </row>
+    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>-261600</v>
+      <c r="D35" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E35" s="3">
-        <v>-196700</v>
+        <v>-263400</v>
       </c>
       <c r="F35" s="3">
-        <v>-74700</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>3</v>
+        <v>-198000</v>
+      </c>
+      <c r="G35" s="3">
+        <v>-75200</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1494,29 +1572,32 @@
       <c r="K35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L35" s="3"/>
-    </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M35" s="3"/>
+    </row>
+    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1529,9 +1610,12 @@
       <c r="K38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L38" s="2"/>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M38" s="2"/>
+    </row>
+    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1544,8 +1628,9 @@
       <c r="J39" s="3"/>
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
-    </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M39" s="3"/>
+    </row>
+    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1558,22 +1643,23 @@
       <c r="J40" s="3"/>
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-    </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M40" s="3"/>
+    </row>
+    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>118800</v>
+        <v>78000</v>
       </c>
       <c r="E41" s="3">
-        <v>121200</v>
+        <v>119600</v>
       </c>
       <c r="F41" s="3">
-        <v>100800</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>3</v>
+        <v>122100</v>
+      </c>
+      <c r="G41" s="3">
+        <v>101500</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1587,53 +1673,59 @@
       <c r="K41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L41" s="3"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M41" s="3"/>
+    </row>
+    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
-      </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
-      <c r="H42" s="3">
-        <v>0</v>
-      </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
-      <c r="J42" s="3">
-        <v>0</v>
+        <v>19200</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
-      <c r="L42" s="3"/>
-    </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3"/>
+    </row>
+    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>474800</v>
+        <v>272500</v>
       </c>
       <c r="E43" s="3">
-        <v>156300</v>
+        <v>478000</v>
       </c>
       <c r="F43" s="3">
-        <v>148000</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>3</v>
+        <v>157400</v>
+      </c>
+      <c r="G43" s="3">
+        <v>149000</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1644,26 +1736,29 @@
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3"/>
-    </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L43" s="3">
+        <v>0</v>
+      </c>
+      <c r="M43" s="3"/>
+    </row>
+    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>43400</v>
+        <v>22400</v>
       </c>
       <c r="E44" s="3">
-        <v>30800</v>
+        <v>43700</v>
       </c>
       <c r="F44" s="3">
-        <v>32300</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>3</v>
+        <v>31000</v>
+      </c>
+      <c r="G44" s="3">
+        <v>32500</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1674,26 +1769,29 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3"/>
-    </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="3">
+        <v>0</v>
+      </c>
+      <c r="M44" s="3"/>
+    </row>
+    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>94700</v>
+        <v>65200</v>
       </c>
       <c r="E45" s="3">
-        <v>30800</v>
+        <v>95400</v>
       </c>
       <c r="F45" s="3">
-        <v>54100</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>3</v>
+        <v>31000</v>
+      </c>
+      <c r="G45" s="3">
+        <v>54500</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1707,23 +1805,26 @@
       <c r="K45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L45" s="3"/>
-    </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M45" s="3"/>
+    </row>
+    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>532100</v>
+        <v>457200</v>
       </c>
       <c r="E46" s="3">
-        <v>339200</v>
+        <v>535700</v>
       </c>
       <c r="F46" s="3">
-        <v>335200</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>3</v>
+        <v>341500</v>
+      </c>
+      <c r="G46" s="3">
+        <v>337500</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1737,24 +1838,27 @@
       <c r="K46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L46" s="3"/>
-    </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M46" s="3"/>
+    </row>
+    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>48900</v>
+        <v>41800</v>
       </c>
       <c r="E47" s="3">
-        <v>187000</v>
+        <v>49200</v>
       </c>
       <c r="F47" s="3">
+        <v>188200</v>
+      </c>
+      <c r="G47" s="3">
         <v>400</v>
       </c>
-      <c r="G47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1764,26 +1868,29 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
-      <c r="L47" s="3"/>
-    </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
+        <v>0</v>
+      </c>
+      <c r="M47" s="3"/>
+    </row>
+    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>61200</v>
+        <v>34200</v>
       </c>
       <c r="E48" s="3">
-        <v>14200</v>
+        <v>61600</v>
       </c>
       <c r="F48" s="3">
-        <v>14600</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>3</v>
+        <v>14300</v>
+      </c>
+      <c r="G48" s="3">
+        <v>14700</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1794,26 +1901,29 @@
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K48" s="3">
-        <v>0</v>
-      </c>
-      <c r="L48" s="3"/>
-    </row>
-    <row r="49" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L48" s="3">
+        <v>0</v>
+      </c>
+      <c r="M48" s="3"/>
+    </row>
+    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>24900</v>
+      </c>
+      <c r="E49" s="3">
         <v>11300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4300</v>
       </c>
-      <c r="F49" s="3">
-        <v>4100</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>3</v>
+      <c r="G49" s="3">
+        <v>4200</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -1824,12 +1934,15 @@
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K49" s="3">
-        <v>0</v>
-      </c>
-      <c r="L49" s="3"/>
-    </row>
-    <row r="50" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L49" s="3">
+        <v>0</v>
+      </c>
+      <c r="M49" s="3"/>
+    </row>
+    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1857,9 +1970,12 @@
       <c r="K50" s="3">
         <v>0</v>
       </c>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L50" s="3">
+        <v>0</v>
+      </c>
+      <c r="M50" s="3"/>
+    </row>
+    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -1887,24 +2003,27 @@
       <c r="K51" s="3">
         <v>0</v>
       </c>
-      <c r="L51" s="3"/>
-    </row>
-    <row r="52" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L51" s="3">
+        <v>0</v>
+      </c>
+      <c r="M51" s="3"/>
+    </row>
+    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>33100</v>
+        <v>35100</v>
       </c>
       <c r="E52" s="3">
+        <v>33300</v>
+      </c>
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>1600</v>
       </c>
-      <c r="G52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
       </c>
@@ -1917,9 +2036,12 @@
       <c r="K52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L52" s="3"/>
-    </row>
-    <row r="53" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M52" s="3"/>
+    </row>
+    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -1947,23 +2069,26 @@
       <c r="K53" s="3">
         <v>0</v>
       </c>
-      <c r="L53" s="3"/>
-    </row>
-    <row r="54" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L53" s="3">
+        <v>0</v>
+      </c>
+      <c r="M53" s="3"/>
+    </row>
+    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>653300</v>
+        <v>593300</v>
       </c>
       <c r="E54" s="3">
-        <v>547700</v>
+        <v>657700</v>
       </c>
       <c r="F54" s="3">
-        <v>356000</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>3</v>
+        <v>551500</v>
+      </c>
+      <c r="G54" s="3">
+        <v>358400</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -1977,9 +2102,12 @@
       <c r="K54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L54" s="3"/>
-    </row>
-    <row r="55" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M54" s="3"/>
+    </row>
+    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -1992,8 +2120,9 @@
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
-    </row>
-    <row r="56" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M55" s="3"/>
+    </row>
+    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2006,22 +2135,23 @@
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
-    </row>
-    <row r="57" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>232900</v>
+        <v>291500</v>
       </c>
       <c r="E57" s="3">
-        <v>105100</v>
+        <v>234500</v>
       </c>
       <c r="F57" s="3">
-        <v>147400</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>3</v>
+        <v>105900</v>
+      </c>
+      <c r="G57" s="3">
+        <v>148400</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2032,26 +2162,29 @@
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3"/>
-    </row>
-    <row r="58" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L57" s="3">
+        <v>0</v>
+      </c>
+      <c r="M57" s="3"/>
+    </row>
+    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>143400</v>
+        <v>168200</v>
       </c>
       <c r="E58" s="3">
-        <v>146300</v>
+        <v>144400</v>
       </c>
       <c r="F58" s="3">
-        <v>82500</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>3</v>
+        <v>147300</v>
+      </c>
+      <c r="G58" s="3">
+        <v>83100</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2065,23 +2198,26 @@
       <c r="K58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L58" s="3"/>
-    </row>
-    <row r="59" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M58" s="3"/>
+    </row>
+    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>268000</v>
+        <v>126300</v>
       </c>
       <c r="E59" s="3">
-        <v>166000</v>
+        <v>269800</v>
       </c>
       <c r="F59" s="3">
-        <v>221300</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>3</v>
+        <v>167100</v>
+      </c>
+      <c r="G59" s="3">
+        <v>222800</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2095,23 +2231,26 @@
       <c r="K59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L59" s="3"/>
-    </row>
-    <row r="60" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M59" s="3"/>
+    </row>
+    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>542300</v>
+        <v>586000</v>
       </c>
       <c r="E60" s="3">
-        <v>417400</v>
+        <v>546000</v>
       </c>
       <c r="F60" s="3">
-        <v>451200</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>3</v>
+        <v>420200</v>
+      </c>
+      <c r="G60" s="3">
+        <v>454300</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2125,23 +2264,26 @@
       <c r="K60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L60" s="3"/>
-    </row>
-    <row r="61" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M60" s="3"/>
+    </row>
+    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>60700</v>
+        <v>63400</v>
       </c>
       <c r="E61" s="3">
-        <v>0</v>
+        <v>61200</v>
       </c>
       <c r="F61" s="3">
-        <v>107100</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>0</v>
+        <v>107800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2155,23 +2297,26 @@
       <c r="K61" s="3">
         <v>0</v>
       </c>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L61" s="3">
+        <v>0</v>
+      </c>
+      <c r="M61" s="3"/>
+    </row>
+    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>55000</v>
+        <v>47300</v>
       </c>
       <c r="E62" s="3">
-        <v>67600</v>
+        <v>55300</v>
       </c>
       <c r="F62" s="3">
-        <v>50600</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>3</v>
+        <v>68000</v>
+      </c>
+      <c r="G62" s="3">
+        <v>51000</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2185,9 +2330,12 @@
       <c r="K62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L62" s="3"/>
-    </row>
-    <row r="63" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M62" s="3"/>
+    </row>
+    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2215,9 +2363,12 @@
       <c r="K63" s="3">
         <v>0</v>
       </c>
-      <c r="L63" s="3"/>
-    </row>
-    <row r="64" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L63" s="3">
+        <v>0</v>
+      </c>
+      <c r="M63" s="3"/>
+    </row>
+    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2245,9 +2396,12 @@
       <c r="K64" s="3">
         <v>0</v>
       </c>
-      <c r="L64" s="3"/>
-    </row>
-    <row r="65" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L64" s="3">
+        <v>0</v>
+      </c>
+      <c r="M64" s="3"/>
+    </row>
+    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2275,23 +2429,26 @@
       <c r="K65" s="3">
         <v>0</v>
       </c>
-      <c r="L65" s="3"/>
-    </row>
-    <row r="66" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L65" s="3">
+        <v>0</v>
+      </c>
+      <c r="M65" s="3"/>
+    </row>
+    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>680400</v>
+        <v>721400</v>
       </c>
       <c r="E66" s="3">
-        <v>488400</v>
+        <v>685000</v>
       </c>
       <c r="F66" s="3">
-        <v>610500</v>
-      </c>
-      <c r="G66" s="3" t="s">
-        <v>3</v>
+        <v>491700</v>
+      </c>
+      <c r="G66" s="3">
+        <v>614600</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2305,9 +2462,12 @@
       <c r="K66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L66" s="3"/>
-    </row>
-    <row r="67" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M66" s="3"/>
+    </row>
+    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2320,8 +2480,9 @@
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
-    </row>
-    <row r="68" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="M67" s="3"/>
+    </row>
+    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2349,9 +2510,12 @@
       <c r="K68" s="3">
         <v>0</v>
       </c>
-      <c r="L68" s="3"/>
-    </row>
-    <row r="69" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L68" s="3">
+        <v>0</v>
+      </c>
+      <c r="M68" s="3"/>
+    </row>
+    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2379,9 +2543,12 @@
       <c r="K69" s="3">
         <v>0</v>
       </c>
-      <c r="L69" s="3"/>
-    </row>
-    <row r="70" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L69" s="3">
+        <v>0</v>
+      </c>
+      <c r="M69" s="3"/>
+    </row>
+    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2389,13 +2556,13 @@
         <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>647900</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>174600</v>
+        <v>652300</v>
       </c>
       <c r="G70" s="3">
-        <v>0</v>
+        <v>175800</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2409,9 +2576,12 @@
       <c r="K70" s="3">
         <v>0</v>
       </c>
-      <c r="L70" s="3"/>
-    </row>
-    <row r="71" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3"/>
+    </row>
+    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2439,23 +2609,26 @@
       <c r="K71" s="3">
         <v>0</v>
       </c>
-      <c r="L71" s="3"/>
-    </row>
-    <row r="72" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L71" s="3">
+        <v>0</v>
+      </c>
+      <c r="M71" s="3"/>
+    </row>
+    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-791200</v>
+        <v>-927300</v>
       </c>
       <c r="E72" s="3">
-        <v>-589400</v>
+        <v>-796600</v>
       </c>
       <c r="F72" s="3">
-        <v>-452200</v>
-      </c>
-      <c r="G72" s="3" t="s">
-        <v>3</v>
+        <v>-593400</v>
+      </c>
+      <c r="G72" s="3">
+        <v>-455200</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2469,9 +2642,12 @@
       <c r="K72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L72" s="3"/>
-    </row>
-    <row r="73" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M72" s="3"/>
+    </row>
+    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2499,9 +2675,12 @@
       <c r="K73" s="3">
         <v>0</v>
       </c>
-      <c r="L73" s="3"/>
-    </row>
-    <row r="74" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L73" s="3">
+        <v>0</v>
+      </c>
+      <c r="M73" s="3"/>
+    </row>
+    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2529,9 +2708,12 @@
       <c r="K74" s="3">
         <v>0</v>
       </c>
-      <c r="L74" s="3"/>
-    </row>
-    <row r="75" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L74" s="3">
+        <v>0</v>
+      </c>
+      <c r="M74" s="3"/>
+    </row>
+    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2559,23 +2741,26 @@
       <c r="K75" s="3">
         <v>0</v>
       </c>
-      <c r="L75" s="3"/>
-    </row>
-    <row r="76" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L75" s="3">
+        <v>0</v>
+      </c>
+      <c r="M75" s="3"/>
+    </row>
+    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-27100</v>
+        <v>-128100</v>
       </c>
       <c r="E76" s="3">
-        <v>-588500</v>
+        <v>-27300</v>
       </c>
       <c r="F76" s="3">
-        <v>-429100</v>
-      </c>
-      <c r="G76" s="3" t="s">
-        <v>3</v>
+        <v>-592500</v>
+      </c>
+      <c r="G76" s="3">
+        <v>-432000</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2589,9 +2774,12 @@
       <c r="K76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L76" s="3"/>
-    </row>
-    <row r="77" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M76" s="3"/>
+    </row>
+    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2619,29 +2807,32 @@
       <c r="K77" s="3">
         <v>0</v>
       </c>
-      <c r="L77" s="3"/>
-    </row>
-    <row r="79" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="L77" s="3">
+        <v>0</v>
+      </c>
+      <c r="M77" s="3"/>
+    </row>
+    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="H80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2654,23 +2845,26 @@
       <c r="K80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="L80" s="2"/>
-    </row>
-    <row r="81" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="M80" s="2"/>
+    </row>
+    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>-261600</v>
+      <c r="D81" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E81" s="3">
-        <v>-196700</v>
+        <v>-263400</v>
       </c>
       <c r="F81" s="3">
-        <v>-74700</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>3</v>
+        <v>-198000</v>
+      </c>
+      <c r="G81" s="3">
+        <v>-75200</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2684,9 +2878,12 @@
       <c r="K81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L81" s="3"/>
-    </row>
-    <row r="82" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M81" s="3"/>
+    </row>
+    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2699,22 +2896,23 @@
       <c r="J82" s="3"/>
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
-    </row>
-    <row r="83" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M82" s="3"/>
+    </row>
+    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>9300</v>
+      <c r="D83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E83" s="3">
+        <v>9400</v>
+      </c>
+      <c r="F83" s="3">
         <v>9000</v>
       </c>
-      <c r="F83" s="3">
-        <v>8100</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>3</v>
+      <c r="G83" s="3">
+        <v>8200</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -2725,12 +2923,15 @@
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3"/>
-    </row>
-    <row r="84" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L83" s="3">
+        <v>0</v>
+      </c>
+      <c r="M83" s="3"/>
+    </row>
+    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2758,9 +2959,12 @@
       <c r="K84" s="3">
         <v>0</v>
       </c>
-      <c r="L84" s="3"/>
-    </row>
-    <row r="85" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L84" s="3">
+        <v>0</v>
+      </c>
+      <c r="M84" s="3"/>
+    </row>
+    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2788,9 +2992,12 @@
       <c r="K85" s="3">
         <v>0</v>
       </c>
-      <c r="L85" s="3"/>
-    </row>
-    <row r="86" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L85" s="3">
+        <v>0</v>
+      </c>
+      <c r="M85" s="3"/>
+    </row>
+    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -2818,9 +3025,12 @@
       <c r="K86" s="3">
         <v>0</v>
       </c>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L86" s="3">
+        <v>0</v>
+      </c>
+      <c r="M86" s="3"/>
+    </row>
+    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -2848,9 +3058,12 @@
       <c r="K87" s="3">
         <v>0</v>
       </c>
-      <c r="L87" s="3"/>
-    </row>
-    <row r="88" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L87" s="3">
+        <v>0</v>
+      </c>
+      <c r="M87" s="3"/>
+    </row>
+    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -2878,23 +3091,26 @@
       <c r="K88" s="3">
         <v>0</v>
       </c>
-      <c r="L88" s="3"/>
-    </row>
-    <row r="89" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L88" s="3">
+        <v>0</v>
+      </c>
+      <c r="M88" s="3"/>
+    </row>
+    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
-        <v>-56000</v>
+      <c r="D89" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E89" s="3">
-        <v>-120500</v>
+        <v>-56400</v>
       </c>
       <c r="F89" s="3">
-        <v>-50800</v>
-      </c>
-      <c r="G89" s="3" t="s">
-        <v>3</v>
+        <v>-121300</v>
+      </c>
+      <c r="G89" s="3">
+        <v>-51200</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -2908,9 +3124,12 @@
       <c r="K89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L89" s="3"/>
-    </row>
-    <row r="90" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M89" s="3"/>
+    </row>
+    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -2923,22 +3142,23 @@
       <c r="J90" s="3"/>
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
-    </row>
-    <row r="91" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M90" s="3"/>
+    </row>
+    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>-17600</v>
+      <c r="D91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E91" s="3">
-        <v>-10900</v>
+        <v>-17800</v>
       </c>
       <c r="F91" s="3">
-        <v>-9500</v>
-      </c>
-      <c r="G91" s="3" t="s">
-        <v>3</v>
+        <v>-11000</v>
+      </c>
+      <c r="G91" s="3">
+        <v>-9600</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -2949,12 +3169,15 @@
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3"/>
-    </row>
-    <row r="92" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L91" s="3">
+        <v>0</v>
+      </c>
+      <c r="M91" s="3"/>
+    </row>
+    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -2982,9 +3205,12 @@
       <c r="K92" s="3">
         <v>0</v>
       </c>
-      <c r="L92" s="3"/>
-    </row>
-    <row r="93" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L92" s="3">
+        <v>0</v>
+      </c>
+      <c r="M92" s="3"/>
+    </row>
+    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3012,23 +3238,26 @@
       <c r="K93" s="3">
         <v>0</v>
       </c>
-      <c r="L93" s="3"/>
-    </row>
-    <row r="94" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L93" s="3">
+        <v>0</v>
+      </c>
+      <c r="M93" s="3"/>
+    </row>
+    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
-        <v>-39100</v>
+      <c r="D94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E94" s="3">
-        <v>-192100</v>
+        <v>-39400</v>
       </c>
       <c r="F94" s="3">
-        <v>-12600</v>
-      </c>
-      <c r="G94" s="3" t="s">
-        <v>3</v>
+        <v>-193400</v>
+      </c>
+      <c r="G94" s="3">
+        <v>-12700</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3042,9 +3271,12 @@
       <c r="K94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L94" s="3"/>
-    </row>
-    <row r="95" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M94" s="3"/>
+    </row>
+    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3057,8 +3289,9 @@
       <c r="J95" s="3"/>
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
-    </row>
-    <row r="96" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="M95" s="3"/>
+    </row>
+    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3086,9 +3319,12 @@
       <c r="K96" s="3">
         <v>0</v>
       </c>
-      <c r="L96" s="3"/>
-    </row>
-    <row r="97" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3"/>
+    </row>
+    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3116,9 +3352,12 @@
       <c r="K97" s="3">
         <v>0</v>
       </c>
-      <c r="L97" s="3"/>
-    </row>
-    <row r="98" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L97" s="3">
+        <v>0</v>
+      </c>
+      <c r="M97" s="3"/>
+    </row>
+    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3146,9 +3385,12 @@
       <c r="K98" s="3">
         <v>0</v>
       </c>
-      <c r="L98" s="3"/>
-    </row>
-    <row r="99" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L98" s="3">
+        <v>0</v>
+      </c>
+      <c r="M98" s="3"/>
+    </row>
+    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3176,23 +3418,26 @@
       <c r="K99" s="3">
         <v>0</v>
       </c>
-      <c r="L99" s="3"/>
-    </row>
-    <row r="100" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L99" s="3">
+        <v>0</v>
+      </c>
+      <c r="M99" s="3"/>
+    </row>
+    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
-        <v>74300</v>
+      <c r="D100" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E100" s="3">
-        <v>302800</v>
+        <v>74800</v>
       </c>
       <c r="F100" s="3">
-        <v>157200</v>
-      </c>
-      <c r="G100" s="3" t="s">
-        <v>3</v>
+        <v>304800</v>
+      </c>
+      <c r="G100" s="3">
+        <v>158200</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3206,24 +3451,27 @@
       <c r="K100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L100" s="3"/>
-    </row>
-    <row r="101" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="L100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M100" s="3"/>
+    </row>
+    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>4000</v>
       </c>
-      <c r="E101" s="3">
-        <v>-4400</v>
-      </c>
       <c r="F101" s="3">
+        <v>-4500</v>
+      </c>
+      <c r="G101" s="3">
         <v>-1400</v>
       </c>
-      <c r="G101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3233,26 +3481,29 @@
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
-      <c r="L101" s="3"/>
-    </row>
-    <row r="102" spans="3:12" x14ac:dyDescent="0.2">
+      <c r="K101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3"/>
+    </row>
+    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3">
-        <v>-16900</v>
+      <c r="D102" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E102" s="3">
-        <v>-14200</v>
+        <v>-17000</v>
       </c>
       <c r="F102" s="3">
-        <v>92400</v>
-      </c>
-      <c r="G102" s="3" t="s">
-        <v>3</v>
+        <v>-14300</v>
+      </c>
+      <c r="G102" s="3">
+        <v>93000</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>
@@ -3266,7 +3517,10 @@
       <c r="K102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L102" s="3"/>
+      <c r="L102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
   <si>
     <t>ECX</t>
   </si>
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>648700</v>
+        <v>644700</v>
       </c>
       <c r="E8" s="3">
-        <v>494500</v>
+        <v>492100</v>
       </c>
       <c r="F8" s="3">
-        <v>386300</v>
+        <v>384000</v>
       </c>
       <c r="G8" s="3">
-        <v>311600</v>
+        <v>309600</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -748,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>472100</v>
+        <v>469200</v>
       </c>
       <c r="E9" s="3">
-        <v>356800</v>
+        <v>354800</v>
       </c>
       <c r="F9" s="3">
-        <v>272700</v>
+        <v>271100</v>
       </c>
       <c r="G9" s="3">
-        <v>234900</v>
+        <v>233400</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>176500</v>
+        <v>175500</v>
       </c>
       <c r="E10" s="3">
-        <v>137700</v>
+        <v>137300</v>
       </c>
       <c r="F10" s="3">
-        <v>113600</v>
+        <v>112900</v>
       </c>
       <c r="G10" s="3">
-        <v>76700</v>
+        <v>76200</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -829,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>175800</v>
+        <v>168500</v>
       </c>
       <c r="E12" s="3">
-        <v>164400</v>
+        <v>179800</v>
       </c>
       <c r="F12" s="3">
-        <v>164000</v>
+        <v>163000</v>
       </c>
       <c r="G12" s="3">
-        <v>94000</v>
+        <v>93400</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -895,10 +895,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="E14" s="3">
-        <v>-10000</v>
+        <v>-9900</v>
       </c>
       <c r="F14" s="3">
         <v>-1500</v>
@@ -927,14 +927,14 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>10700</v>
       </c>
       <c r="E15" s="3">
-        <v>9300</v>
+        <v>15300</v>
       </c>
       <c r="F15" s="3">
-        <v>8800</v>
+        <v>13300</v>
       </c>
       <c r="G15" s="3">
         <v>7900</v>
@@ -972,17 +972,17 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>771500</v>
       </c>
       <c r="E17" s="3">
-        <v>688400</v>
+        <v>707100</v>
       </c>
       <c r="F17" s="3">
-        <v>521300</v>
+        <v>520700</v>
       </c>
       <c r="G17" s="3">
-        <v>371400</v>
+        <v>369100</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1005,17 +1005,17 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-126800</v>
       </c>
       <c r="E18" s="3">
-        <v>-193800</v>
+        <v>-215000</v>
       </c>
       <c r="F18" s="3">
-        <v>-135000</v>
+        <v>-136700</v>
       </c>
       <c r="G18" s="3">
-        <v>-59800</v>
+        <v>-59500</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1053,14 +1053,14 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>-3000</v>
       </c>
       <c r="E20" s="3">
-        <v>-10300</v>
+        <v>3100</v>
       </c>
       <c r="F20" s="3">
-        <v>-11000</v>
+        <v>-6700</v>
       </c>
       <c r="G20" s="3">
         <v>6900</v>
@@ -1086,17 +1086,17 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-118000</v>
       </c>
       <c r="E21" s="3">
-        <v>-194700</v>
+        <v>-201600</v>
       </c>
       <c r="F21" s="3">
-        <v>-137000</v>
+        <v>-134500</v>
       </c>
       <c r="G21" s="3">
-        <v>-44700</v>
+        <v>-44500</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1123,10 +1123,10 @@
         <v>11000</v>
       </c>
       <c r="E22" s="3">
-        <v>7100</v>
+        <v>6200</v>
       </c>
       <c r="F22" s="3">
-        <v>18300</v>
+        <v>18200</v>
       </c>
       <c r="G22" s="3">
         <v>8200</v>
@@ -1153,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-141600</v>
+        <v>-140800</v>
       </c>
       <c r="E23" s="3">
-        <v>-211300</v>
+        <v>-218000</v>
       </c>
       <c r="F23" s="3">
-        <v>-164300</v>
+        <v>-161600</v>
       </c>
       <c r="G23" s="3">
-        <v>-61100</v>
+        <v>-60800</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1185,14 +1185,14 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>3</v>
+      <c r="D24" s="3">
+        <v>-500</v>
       </c>
       <c r="E24" s="3">
-        <v>3000</v>
+        <v>4000</v>
       </c>
       <c r="F24" s="3">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1251,17 +1251,17 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-140300</v>
       </c>
       <c r="E26" s="3">
-        <v>-214300</v>
+        <v>-222000</v>
       </c>
       <c r="F26" s="3">
-        <v>-164800</v>
+        <v>-162600</v>
       </c>
       <c r="G26" s="3">
-        <v>-61200</v>
+        <v>-60800</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1284,17 +1284,17 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-129900</v>
       </c>
       <c r="E27" s="3">
-        <v>-263400</v>
+        <v>-265200</v>
       </c>
       <c r="F27" s="3">
-        <v>-198000</v>
+        <v>-196000</v>
       </c>
       <c r="G27" s="3">
-        <v>-75200</v>
+        <v>-74700</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1449,14 +1449,14 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>3000</v>
       </c>
       <c r="E32" s="3">
-        <v>10300</v>
+        <v>-3100</v>
       </c>
       <c r="F32" s="3">
-        <v>11000</v>
+        <v>6700</v>
       </c>
       <c r="G32" s="3">
         <v>-6900</v>
@@ -1482,17 +1482,17 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-129900</v>
       </c>
       <c r="E33" s="3">
-        <v>-263400</v>
+        <v>-265200</v>
       </c>
       <c r="F33" s="3">
-        <v>-198000</v>
+        <v>-196000</v>
       </c>
       <c r="G33" s="3">
-        <v>-75200</v>
+        <v>-74700</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1548,17 +1548,17 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-129900</v>
       </c>
       <c r="E35" s="3">
-        <v>-263400</v>
+        <v>-265200</v>
       </c>
       <c r="F35" s="3">
-        <v>-198000</v>
+        <v>-196000</v>
       </c>
       <c r="G35" s="3">
-        <v>-75200</v>
+        <v>-74700</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1650,16 +1650,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>78000</v>
+        <v>77500</v>
       </c>
       <c r="E41" s="3">
-        <v>119600</v>
+        <v>118900</v>
       </c>
       <c r="F41" s="3">
-        <v>122100</v>
+        <v>121300</v>
       </c>
       <c r="G41" s="3">
-        <v>101500</v>
+        <v>100800</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19200</v>
+        <v>19000</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -1716,16 +1716,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>272500</v>
+        <v>285300</v>
       </c>
       <c r="E43" s="3">
-        <v>478000</v>
+        <v>475000</v>
       </c>
       <c r="F43" s="3">
-        <v>157400</v>
+        <v>156400</v>
       </c>
       <c r="G43" s="3">
-        <v>149000</v>
+        <v>148100</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1749,16 +1749,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>22400</v>
+        <v>22200</v>
       </c>
       <c r="E44" s="3">
-        <v>43700</v>
+        <v>43400</v>
       </c>
       <c r="F44" s="3">
-        <v>31000</v>
+        <v>30900</v>
       </c>
       <c r="G44" s="3">
-        <v>32500</v>
+        <v>32300</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1782,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>65200</v>
+        <v>50300</v>
       </c>
       <c r="E45" s="3">
-        <v>95400</v>
+        <v>94800</v>
       </c>
       <c r="F45" s="3">
-        <v>31000</v>
+        <v>30800</v>
       </c>
       <c r="G45" s="3">
-        <v>54500</v>
+        <v>54200</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1815,16 +1815,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>457200</v>
+        <v>454400</v>
       </c>
       <c r="E46" s="3">
-        <v>535700</v>
+        <v>532400</v>
       </c>
       <c r="F46" s="3">
-        <v>341500</v>
+        <v>339400</v>
       </c>
       <c r="G46" s="3">
-        <v>337500</v>
+        <v>335400</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1848,13 +1848,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>41800</v>
+        <v>41600</v>
       </c>
       <c r="E47" s="3">
-        <v>49200</v>
+        <v>48900</v>
       </c>
       <c r="F47" s="3">
-        <v>188200</v>
+        <v>187100</v>
       </c>
       <c r="G47" s="3">
         <v>400</v>
@@ -1881,10 +1881,10 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34200</v>
+        <v>34000</v>
       </c>
       <c r="E48" s="3">
-        <v>61600</v>
+        <v>61200</v>
       </c>
       <c r="F48" s="3">
         <v>14300</v>
@@ -1914,7 +1914,7 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>24900</v>
+        <v>24800</v>
       </c>
       <c r="E49" s="3">
         <v>11300</v>
@@ -2013,10 +2013,10 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>35100</v>
+        <v>34900</v>
       </c>
       <c r="E52" s="3">
-        <v>33300</v>
+        <v>33100</v>
       </c>
       <c r="F52" s="3">
         <v>3000</v>
@@ -2079,16 +2079,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>593300</v>
+        <v>589600</v>
       </c>
       <c r="E54" s="3">
-        <v>657700</v>
+        <v>653600</v>
       </c>
       <c r="F54" s="3">
-        <v>551500</v>
+        <v>548000</v>
       </c>
       <c r="G54" s="3">
-        <v>358400</v>
+        <v>356200</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2142,16 +2142,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>291500</v>
+        <v>289700</v>
       </c>
       <c r="E57" s="3">
-        <v>234500</v>
+        <v>233100</v>
       </c>
       <c r="F57" s="3">
-        <v>105900</v>
+        <v>105200</v>
       </c>
       <c r="G57" s="3">
-        <v>148400</v>
+        <v>147400</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2175,16 +2175,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>168200</v>
+        <v>167200</v>
       </c>
       <c r="E58" s="3">
-        <v>144400</v>
+        <v>143500</v>
       </c>
       <c r="F58" s="3">
-        <v>147300</v>
+        <v>146400</v>
       </c>
       <c r="G58" s="3">
-        <v>83100</v>
+        <v>82600</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>126300</v>
+        <v>125600</v>
       </c>
       <c r="E59" s="3">
-        <v>269800</v>
+        <v>268100</v>
       </c>
       <c r="F59" s="3">
-        <v>167100</v>
+        <v>166000</v>
       </c>
       <c r="G59" s="3">
-        <v>222800</v>
+        <v>221400</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2241,16 +2241,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>586000</v>
+        <v>582400</v>
       </c>
       <c r="E60" s="3">
-        <v>546000</v>
+        <v>542600</v>
       </c>
       <c r="F60" s="3">
-        <v>420200</v>
+        <v>417600</v>
       </c>
       <c r="G60" s="3">
-        <v>454300</v>
+        <v>451500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>63400</v>
+        <v>63000</v>
       </c>
       <c r="E61" s="3">
-        <v>61200</v>
+        <v>60800</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>107800</v>
+        <v>107100</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>47300</v>
+        <v>59500</v>
       </c>
       <c r="E62" s="3">
-        <v>55300</v>
+        <v>55000</v>
       </c>
       <c r="F62" s="3">
-        <v>68000</v>
+        <v>67600</v>
       </c>
       <c r="G62" s="3">
-        <v>51000</v>
+        <v>50700</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2439,16 +2439,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>721400</v>
+        <v>716900</v>
       </c>
       <c r="E66" s="3">
-        <v>685000</v>
+        <v>680800</v>
       </c>
       <c r="F66" s="3">
-        <v>491700</v>
+        <v>488600</v>
       </c>
       <c r="G66" s="3">
-        <v>614600</v>
+        <v>610800</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2559,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>652300</v>
+        <v>648300</v>
       </c>
       <c r="G70" s="3">
-        <v>175800</v>
+        <v>174700</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-927300</v>
+        <v>-921600</v>
       </c>
       <c r="E72" s="3">
-        <v>-796600</v>
+        <v>-791700</v>
       </c>
       <c r="F72" s="3">
-        <v>-593400</v>
+        <v>-589700</v>
       </c>
       <c r="G72" s="3">
-        <v>-455200</v>
+        <v>-452400</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2751,16 +2751,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-128100</v>
+        <v>-127300</v>
       </c>
       <c r="E76" s="3">
-        <v>-27300</v>
+        <v>-27100</v>
       </c>
       <c r="F76" s="3">
-        <v>-592500</v>
+        <v>-588900</v>
       </c>
       <c r="G76" s="3">
-        <v>-432000</v>
+        <v>-429300</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2854,17 +2854,17 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-129900</v>
       </c>
       <c r="E81" s="3">
-        <v>-263400</v>
+        <v>-265200</v>
       </c>
       <c r="F81" s="3">
-        <v>-198000</v>
+        <v>-196000</v>
       </c>
       <c r="G81" s="3">
-        <v>-75200</v>
+        <v>-74700</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2902,17 +2902,17 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>11900</v>
       </c>
       <c r="E83" s="3">
-        <v>9400</v>
+        <v>10300</v>
       </c>
       <c r="F83" s="3">
         <v>9000</v>
       </c>
       <c r="G83" s="3">
-        <v>8200</v>
+        <v>8100</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3100,17 +3100,17 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-171800</v>
       </c>
       <c r="E89" s="3">
-        <v>-56400</v>
+        <v>-63700</v>
       </c>
       <c r="F89" s="3">
-        <v>-121300</v>
+        <v>-125400</v>
       </c>
       <c r="G89" s="3">
-        <v>-51200</v>
+        <v>-50800</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3148,17 +3148,17 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-8600</v>
       </c>
       <c r="E91" s="3">
-        <v>-17800</v>
+        <v>-21700</v>
       </c>
       <c r="F91" s="3">
-        <v>-11000</v>
+        <v>-11800</v>
       </c>
       <c r="G91" s="3">
-        <v>-9600</v>
+        <v>-9500</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3247,17 +3247,17 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>81800</v>
       </c>
       <c r="E94" s="3">
-        <v>-39400</v>
+        <v>-43200</v>
       </c>
       <c r="F94" s="3">
-        <v>-193400</v>
+        <v>-165500</v>
       </c>
       <c r="G94" s="3">
-        <v>-12700</v>
+        <v>-12600</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3427,17 +3427,17 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>41000</v>
       </c>
       <c r="E100" s="3">
-        <v>74800</v>
+        <v>90900</v>
       </c>
       <c r="F100" s="3">
-        <v>304800</v>
+        <v>293300</v>
       </c>
       <c r="G100" s="3">
-        <v>158200</v>
+        <v>157200</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3460,14 +3460,14 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>5700</v>
       </c>
       <c r="E101" s="3">
         <v>4000</v>
       </c>
       <c r="F101" s="3">
-        <v>-4500</v>
+        <v>-4400</v>
       </c>
       <c r="G101" s="3">
         <v>-1400</v>
@@ -3493,17 +3493,17 @@
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D102" s="3" t="s">
-        <v>3</v>
+      <c r="D102" s="3">
+        <v>-43300</v>
       </c>
       <c r="E102" s="3">
-        <v>-17000</v>
+        <v>-12100</v>
       </c>
       <c r="F102" s="3">
-        <v>-14300</v>
+        <v>-2000</v>
       </c>
       <c r="G102" s="3">
-        <v>93000</v>
+        <v>92400</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>644700</v>
+        <v>657800</v>
       </c>
       <c r="E8" s="3">
-        <v>492100</v>
+        <v>502200</v>
       </c>
       <c r="F8" s="3">
-        <v>384000</v>
+        <v>391800</v>
       </c>
       <c r="G8" s="3">
-        <v>309600</v>
+        <v>315900</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -748,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>469200</v>
+        <v>478800</v>
       </c>
       <c r="E9" s="3">
-        <v>354800</v>
+        <v>362100</v>
       </c>
       <c r="F9" s="3">
-        <v>271100</v>
+        <v>276600</v>
       </c>
       <c r="G9" s="3">
-        <v>233400</v>
+        <v>238200</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>175500</v>
+        <v>179000</v>
       </c>
       <c r="E10" s="3">
-        <v>137300</v>
+        <v>140100</v>
       </c>
       <c r="F10" s="3">
-        <v>112900</v>
+        <v>115200</v>
       </c>
       <c r="G10" s="3">
-        <v>76200</v>
+        <v>77700</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -829,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>168500</v>
+        <v>172000</v>
       </c>
       <c r="E12" s="3">
-        <v>179800</v>
+        <v>183400</v>
       </c>
       <c r="F12" s="3">
-        <v>163000</v>
+        <v>166300</v>
       </c>
       <c r="G12" s="3">
-        <v>93400</v>
+        <v>95300</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -898,7 +898,7 @@
         <v>1400</v>
       </c>
       <c r="E14" s="3">
-        <v>-9900</v>
+        <v>-10100</v>
       </c>
       <c r="F14" s="3">
         <v>-1500</v>
@@ -928,16 +928,16 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10700</v>
+        <v>10900</v>
       </c>
       <c r="E15" s="3">
-        <v>15300</v>
+        <v>15600</v>
       </c>
       <c r="F15" s="3">
-        <v>13300</v>
+        <v>13500</v>
       </c>
       <c r="G15" s="3">
-        <v>7900</v>
+        <v>8100</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>3</v>
@@ -973,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>771500</v>
+        <v>787200</v>
       </c>
       <c r="E17" s="3">
-        <v>707100</v>
+        <v>721600</v>
       </c>
       <c r="F17" s="3">
-        <v>520700</v>
+        <v>531300</v>
       </c>
       <c r="G17" s="3">
-        <v>369100</v>
+        <v>376600</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1006,16 +1006,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-126800</v>
+        <v>-129400</v>
       </c>
       <c r="E18" s="3">
-        <v>-215000</v>
+        <v>-219400</v>
       </c>
       <c r="F18" s="3">
-        <v>-136700</v>
+        <v>-139500</v>
       </c>
       <c r="G18" s="3">
-        <v>-59500</v>
+        <v>-60700</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1054,16 +1054,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3000</v>
+        <v>-3100</v>
       </c>
       <c r="E20" s="3">
-        <v>3100</v>
+        <v>3200</v>
       </c>
       <c r="F20" s="3">
-        <v>-6700</v>
+        <v>-6900</v>
       </c>
       <c r="G20" s="3">
-        <v>6900</v>
+        <v>7000</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1087,16 +1087,16 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-118000</v>
+        <v>-120400</v>
       </c>
       <c r="E21" s="3">
-        <v>-201600</v>
+        <v>-205700</v>
       </c>
       <c r="F21" s="3">
-        <v>-134500</v>
+        <v>-137200</v>
       </c>
       <c r="G21" s="3">
-        <v>-44500</v>
+        <v>-45400</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>3</v>
@@ -1120,16 +1120,16 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>11000</v>
+        <v>11200</v>
       </c>
       <c r="E22" s="3">
-        <v>6200</v>
+        <v>6300</v>
       </c>
       <c r="F22" s="3">
-        <v>18200</v>
+        <v>18600</v>
       </c>
       <c r="G22" s="3">
-        <v>8200</v>
+        <v>8300</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1153,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-140800</v>
+        <v>-143600</v>
       </c>
       <c r="E23" s="3">
-        <v>-218000</v>
+        <v>-222500</v>
       </c>
       <c r="F23" s="3">
-        <v>-161600</v>
+        <v>-164900</v>
       </c>
       <c r="G23" s="3">
-        <v>-60800</v>
+        <v>-62000</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1189,10 +1189,10 @@
         <v>-500</v>
       </c>
       <c r="E24" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="F24" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-140300</v>
+        <v>-143100</v>
       </c>
       <c r="E26" s="3">
-        <v>-222000</v>
+        <v>-226600</v>
       </c>
       <c r="F26" s="3">
-        <v>-162600</v>
+        <v>-165900</v>
       </c>
       <c r="G26" s="3">
-        <v>-60800</v>
+        <v>-62000</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1285,16 +1285,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-129900</v>
+        <v>-132500</v>
       </c>
       <c r="E27" s="3">
-        <v>-265200</v>
+        <v>-270600</v>
       </c>
       <c r="F27" s="3">
-        <v>-196000</v>
+        <v>-200000</v>
       </c>
       <c r="G27" s="3">
-        <v>-74700</v>
+        <v>-76300</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1450,16 +1450,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3100</v>
+        <v>-3200</v>
       </c>
       <c r="F32" s="3">
-        <v>6700</v>
+        <v>6900</v>
       </c>
       <c r="G32" s="3">
-        <v>-6900</v>
+        <v>-7000</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1483,16 +1483,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-129900</v>
+        <v>-132500</v>
       </c>
       <c r="E33" s="3">
-        <v>-265200</v>
+        <v>-270600</v>
       </c>
       <c r="F33" s="3">
-        <v>-196000</v>
+        <v>-200000</v>
       </c>
       <c r="G33" s="3">
-        <v>-74700</v>
+        <v>-76300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1549,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-129900</v>
+        <v>-132500</v>
       </c>
       <c r="E35" s="3">
-        <v>-265200</v>
+        <v>-270600</v>
       </c>
       <c r="F35" s="3">
-        <v>-196000</v>
+        <v>-200000</v>
       </c>
       <c r="G35" s="3">
-        <v>-74700</v>
+        <v>-76300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1650,16 +1650,16 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>77500</v>
+        <v>79100</v>
       </c>
       <c r="E41" s="3">
-        <v>118900</v>
+        <v>121300</v>
       </c>
       <c r="F41" s="3">
-        <v>121300</v>
+        <v>123800</v>
       </c>
       <c r="G41" s="3">
-        <v>100800</v>
+        <v>102900</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1683,7 +1683,7 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>19000</v>
+        <v>19400</v>
       </c>
       <c r="E42" s="3" t="s">
         <v>3</v>
@@ -1716,16 +1716,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>285300</v>
+        <v>291100</v>
       </c>
       <c r="E43" s="3">
-        <v>475000</v>
+        <v>484700</v>
       </c>
       <c r="F43" s="3">
-        <v>156400</v>
+        <v>159600</v>
       </c>
       <c r="G43" s="3">
-        <v>148100</v>
+        <v>151100</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1749,16 +1749,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>22200</v>
+        <v>22700</v>
       </c>
       <c r="E44" s="3">
-        <v>43400</v>
+        <v>44300</v>
       </c>
       <c r="F44" s="3">
-        <v>30900</v>
+        <v>31500</v>
       </c>
       <c r="G44" s="3">
-        <v>32300</v>
+        <v>33000</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1782,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>50300</v>
+        <v>51400</v>
       </c>
       <c r="E45" s="3">
-        <v>94800</v>
+        <v>96700</v>
       </c>
       <c r="F45" s="3">
-        <v>30800</v>
+        <v>31400</v>
       </c>
       <c r="G45" s="3">
-        <v>54200</v>
+        <v>55300</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1815,16 +1815,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>454400</v>
+        <v>463600</v>
       </c>
       <c r="E46" s="3">
-        <v>532400</v>
+        <v>543200</v>
       </c>
       <c r="F46" s="3">
-        <v>339400</v>
+        <v>346300</v>
       </c>
       <c r="G46" s="3">
-        <v>335400</v>
+        <v>342300</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1848,13 +1848,13 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>41600</v>
+        <v>42400</v>
       </c>
       <c r="E47" s="3">
-        <v>48900</v>
+        <v>49900</v>
       </c>
       <c r="F47" s="3">
-        <v>187100</v>
+        <v>190900</v>
       </c>
       <c r="G47" s="3">
         <v>400</v>
@@ -1881,16 +1881,16 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34000</v>
+        <v>34700</v>
       </c>
       <c r="E48" s="3">
-        <v>61200</v>
+        <v>62500</v>
       </c>
       <c r="F48" s="3">
-        <v>14300</v>
+        <v>14500</v>
       </c>
       <c r="G48" s="3">
-        <v>14700</v>
+        <v>15000</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1914,13 +1914,13 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>24800</v>
+        <v>25300</v>
       </c>
       <c r="E49" s="3">
-        <v>11300</v>
+        <v>11500</v>
       </c>
       <c r="F49" s="3">
-        <v>4300</v>
+        <v>4400</v>
       </c>
       <c r="G49" s="3">
         <v>4200</v>
@@ -2013,13 +2013,13 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>34900</v>
+        <v>35600</v>
       </c>
       <c r="E52" s="3">
-        <v>33100</v>
+        <v>33800</v>
       </c>
       <c r="F52" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="G52" s="3">
         <v>1600</v>
@@ -2079,16 +2079,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>589600</v>
+        <v>601700</v>
       </c>
       <c r="E54" s="3">
-        <v>653600</v>
+        <v>667000</v>
       </c>
       <c r="F54" s="3">
-        <v>548000</v>
+        <v>559200</v>
       </c>
       <c r="G54" s="3">
-        <v>356200</v>
+        <v>363500</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2142,16 +2142,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>289700</v>
+        <v>295600</v>
       </c>
       <c r="E57" s="3">
-        <v>233100</v>
+        <v>237800</v>
       </c>
       <c r="F57" s="3">
-        <v>105200</v>
+        <v>107400</v>
       </c>
       <c r="G57" s="3">
-        <v>147400</v>
+        <v>150500</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2175,16 +2175,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>167200</v>
+        <v>170600</v>
       </c>
       <c r="E58" s="3">
-        <v>143500</v>
+        <v>146400</v>
       </c>
       <c r="F58" s="3">
-        <v>146400</v>
+        <v>149300</v>
       </c>
       <c r="G58" s="3">
-        <v>82600</v>
+        <v>84300</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>125600</v>
+        <v>128100</v>
       </c>
       <c r="E59" s="3">
-        <v>268100</v>
+        <v>273600</v>
       </c>
       <c r="F59" s="3">
-        <v>166000</v>
+        <v>169400</v>
       </c>
       <c r="G59" s="3">
-        <v>221400</v>
+        <v>225900</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2241,16 +2241,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>582400</v>
+        <v>594300</v>
       </c>
       <c r="E60" s="3">
-        <v>542600</v>
+        <v>553700</v>
       </c>
       <c r="F60" s="3">
-        <v>417600</v>
+        <v>426100</v>
       </c>
       <c r="G60" s="3">
-        <v>451500</v>
+        <v>460700</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>63000</v>
+        <v>64200</v>
       </c>
       <c r="E61" s="3">
-        <v>60800</v>
+        <v>62000</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>107100</v>
+        <v>109300</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>59500</v>
+        <v>60800</v>
       </c>
       <c r="E62" s="3">
-        <v>55000</v>
+        <v>56100</v>
       </c>
       <c r="F62" s="3">
-        <v>67600</v>
+        <v>69000</v>
       </c>
       <c r="G62" s="3">
-        <v>50700</v>
+        <v>51700</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2439,16 +2439,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>716900</v>
+        <v>731600</v>
       </c>
       <c r="E66" s="3">
-        <v>680800</v>
+        <v>694700</v>
       </c>
       <c r="F66" s="3">
-        <v>488600</v>
+        <v>498600</v>
       </c>
       <c r="G66" s="3">
-        <v>610800</v>
+        <v>623300</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2559,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>648300</v>
+        <v>661500</v>
       </c>
       <c r="G70" s="3">
-        <v>174700</v>
+        <v>178300</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-921600</v>
+        <v>-940400</v>
       </c>
       <c r="E72" s="3">
-        <v>-791700</v>
+        <v>-807800</v>
       </c>
       <c r="F72" s="3">
-        <v>-589700</v>
+        <v>-601800</v>
       </c>
       <c r="G72" s="3">
-        <v>-452400</v>
+        <v>-461600</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2751,16 +2751,16 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-127300</v>
+        <v>-129900</v>
       </c>
       <c r="E76" s="3">
-        <v>-27100</v>
+        <v>-27700</v>
       </c>
       <c r="F76" s="3">
-        <v>-588900</v>
+        <v>-600900</v>
       </c>
       <c r="G76" s="3">
-        <v>-429300</v>
+        <v>-438100</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2855,16 +2855,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-129900</v>
+        <v>-132500</v>
       </c>
       <c r="E81" s="3">
-        <v>-265200</v>
+        <v>-270600</v>
       </c>
       <c r="F81" s="3">
-        <v>-196000</v>
+        <v>-200000</v>
       </c>
       <c r="G81" s="3">
-        <v>-74700</v>
+        <v>-76300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2903,16 +2903,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>11900</v>
+        <v>12100</v>
       </c>
       <c r="E83" s="3">
-        <v>10300</v>
+        <v>10500</v>
       </c>
       <c r="F83" s="3">
-        <v>9000</v>
+        <v>9200</v>
       </c>
       <c r="G83" s="3">
-        <v>8100</v>
+        <v>8300</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3101,16 +3101,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-171800</v>
+        <v>-175300</v>
       </c>
       <c r="E89" s="3">
-        <v>-63700</v>
+        <v>-65000</v>
       </c>
       <c r="F89" s="3">
-        <v>-125400</v>
+        <v>-127900</v>
       </c>
       <c r="G89" s="3">
-        <v>-50800</v>
+        <v>-51900</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3149,16 +3149,16 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-8600</v>
+        <v>-8800</v>
       </c>
       <c r="E91" s="3">
-        <v>-21700</v>
+        <v>-22200</v>
       </c>
       <c r="F91" s="3">
-        <v>-11800</v>
+        <v>-12100</v>
       </c>
       <c r="G91" s="3">
-        <v>-9500</v>
+        <v>-9700</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3248,16 +3248,16 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>81800</v>
+        <v>83500</v>
       </c>
       <c r="E94" s="3">
-        <v>-43200</v>
+        <v>-44100</v>
       </c>
       <c r="F94" s="3">
-        <v>-165500</v>
+        <v>-168900</v>
       </c>
       <c r="G94" s="3">
-        <v>-12600</v>
+        <v>-12800</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3428,16 +3428,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>41000</v>
+        <v>41800</v>
       </c>
       <c r="E100" s="3">
-        <v>90900</v>
+        <v>92700</v>
       </c>
       <c r="F100" s="3">
-        <v>293300</v>
+        <v>299300</v>
       </c>
       <c r="G100" s="3">
-        <v>157200</v>
+        <v>160500</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3461,13 +3461,13 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>5700</v>
+        <v>5800</v>
       </c>
       <c r="E101" s="3">
-        <v>4000</v>
+        <v>4100</v>
       </c>
       <c r="F101" s="3">
-        <v>-4400</v>
+        <v>-4500</v>
       </c>
       <c r="G101" s="3">
         <v>-1400</v>
@@ -3494,16 +3494,16 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-43300</v>
+        <v>-44100</v>
       </c>
       <c r="E102" s="3">
-        <v>-12100</v>
+        <v>-12400</v>
       </c>
       <c r="F102" s="3">
-        <v>-2000</v>
+        <v>-2100</v>
       </c>
       <c r="G102" s="3">
-        <v>92400</v>
+        <v>94300</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>ECX</t>
   </si>
@@ -715,16 +715,16 @@
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>657800</v>
+        <v>658000</v>
       </c>
       <c r="E8" s="3">
-        <v>502200</v>
+        <v>516400</v>
       </c>
       <c r="F8" s="3">
-        <v>391800</v>
+        <v>437500</v>
       </c>
       <c r="G8" s="3">
-        <v>315900</v>
+        <v>343300</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>3</v>
@@ -748,16 +748,16 @@
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>478800</v>
+        <v>478900</v>
       </c>
       <c r="E9" s="3">
-        <v>362100</v>
+        <v>372300</v>
       </c>
       <c r="F9" s="3">
-        <v>276600</v>
+        <v>308800</v>
       </c>
       <c r="G9" s="3">
-        <v>238200</v>
+        <v>258800</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>3</v>
@@ -781,16 +781,16 @@
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>179000</v>
+        <v>179100</v>
       </c>
       <c r="E10" s="3">
-        <v>140100</v>
+        <v>144100</v>
       </c>
       <c r="F10" s="3">
-        <v>115200</v>
+        <v>128600</v>
       </c>
       <c r="G10" s="3">
-        <v>77700</v>
+        <v>84500</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>3</v>
@@ -829,16 +829,16 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>172000</v>
+        <v>174000</v>
       </c>
       <c r="E12" s="3">
-        <v>183400</v>
+        <v>188700</v>
       </c>
       <c r="F12" s="3">
-        <v>166300</v>
+        <v>190400</v>
       </c>
       <c r="G12" s="3">
-        <v>95300</v>
+        <v>108100</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>3</v>
@@ -895,16 +895,16 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1400</v>
+        <v>4600</v>
       </c>
       <c r="E14" s="3">
-        <v>-10100</v>
+        <v>-16700</v>
       </c>
       <c r="F14" s="3">
-        <v>-1500</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
+        <v>-1700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
@@ -928,25 +928,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>10900</v>
+        <v>12100</v>
       </c>
       <c r="E15" s="3">
-        <v>15600</v>
+        <v>7300</v>
       </c>
       <c r="F15" s="3">
-        <v>13500</v>
+        <v>6800</v>
       </c>
       <c r="G15" s="3">
-        <v>8100</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>3</v>
+        <v>5900</v>
+      </c>
+      <c r="H15" s="3">
+        <v>0</v>
+      </c>
+      <c r="I15" s="3">
+        <v>0</v>
+      </c>
+      <c r="J15" s="3">
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="s">
         <v>3</v>
@@ -973,16 +973,16 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>787200</v>
+        <v>786000</v>
       </c>
       <c r="E17" s="3">
-        <v>721600</v>
+        <v>752500</v>
       </c>
       <c r="F17" s="3">
-        <v>531300</v>
+        <v>594900</v>
       </c>
       <c r="G17" s="3">
-        <v>376600</v>
+        <v>409200</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>3</v>
@@ -1006,16 +1006,16 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-129400</v>
+        <v>-128000</v>
       </c>
       <c r="E18" s="3">
-        <v>-219400</v>
+        <v>-236100</v>
       </c>
       <c r="F18" s="3">
-        <v>-139500</v>
+        <v>-157400</v>
       </c>
       <c r="G18" s="3">
-        <v>-60700</v>
+        <v>-65900</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>3</v>
@@ -1054,16 +1054,16 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-3100</v>
+        <v>4200</v>
       </c>
       <c r="E20" s="3">
-        <v>3200</v>
+        <v>4900</v>
       </c>
       <c r="F20" s="3">
-        <v>-6900</v>
+        <v>9800</v>
       </c>
       <c r="G20" s="3">
-        <v>7000</v>
+        <v>-3300</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>3</v>
@@ -1087,25 +1087,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-120400</v>
+        <v>-120100</v>
       </c>
       <c r="E21" s="3">
-        <v>-205700</v>
+        <v>-233700</v>
       </c>
       <c r="F21" s="3">
-        <v>-137200</v>
+        <v>-160400</v>
       </c>
       <c r="G21" s="3">
-        <v>-45400</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>3</v>
+        <v>-56800</v>
+      </c>
+      <c r="H21" s="3">
+        <v>0</v>
+      </c>
+      <c r="I21" s="3">
+        <v>0</v>
+      </c>
+      <c r="J21" s="3">
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="s">
         <v>3</v>
@@ -1123,13 +1123,13 @@
         <v>11200</v>
       </c>
       <c r="E22" s="3">
-        <v>6300</v>
+        <v>6500</v>
       </c>
       <c r="F22" s="3">
-        <v>18600</v>
+        <v>20700</v>
       </c>
       <c r="G22" s="3">
-        <v>8300</v>
+        <v>9100</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>3</v>
@@ -1153,16 +1153,16 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-143600</v>
+        <v>-143700</v>
       </c>
       <c r="E23" s="3">
-        <v>-222500</v>
+        <v>-228800</v>
       </c>
       <c r="F23" s="3">
-        <v>-164900</v>
+        <v>-184200</v>
       </c>
       <c r="G23" s="3">
-        <v>-62000</v>
+        <v>-67400</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>3</v>
@@ -1189,10 +1189,10 @@
         <v>-500</v>
       </c>
       <c r="E24" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F24" s="3">
-        <v>1000</v>
+        <v>1100</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1252,16 +1252,16 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-143100</v>
+        <v>-143200</v>
       </c>
       <c r="E26" s="3">
-        <v>-226600</v>
+        <v>-233000</v>
       </c>
       <c r="F26" s="3">
-        <v>-165900</v>
+        <v>-185200</v>
       </c>
       <c r="G26" s="3">
-        <v>-62000</v>
+        <v>-67400</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>3</v>
@@ -1285,16 +1285,16 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-132500</v>
+        <v>-132600</v>
       </c>
       <c r="E27" s="3">
-        <v>-270600</v>
+        <v>-278200</v>
       </c>
       <c r="F27" s="3">
-        <v>-200000</v>
+        <v>-223300</v>
       </c>
       <c r="G27" s="3">
-        <v>-76300</v>
+        <v>-82900</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>3</v>
@@ -1450,16 +1450,16 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>3100</v>
+        <v>-4200</v>
       </c>
       <c r="E32" s="3">
-        <v>-3200</v>
+        <v>-4900</v>
       </c>
       <c r="F32" s="3">
-        <v>6900</v>
+        <v>-9800</v>
       </c>
       <c r="G32" s="3">
-        <v>-7000</v>
+        <v>3300</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>3</v>
@@ -1483,16 +1483,16 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-132500</v>
+        <v>-132600</v>
       </c>
       <c r="E33" s="3">
-        <v>-270600</v>
+        <v>-226800</v>
       </c>
       <c r="F33" s="3">
-        <v>-200000</v>
+        <v>-184800</v>
       </c>
       <c r="G33" s="3">
-        <v>-76300</v>
+        <v>-67300</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>3</v>
@@ -1549,16 +1549,16 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-132500</v>
+        <v>-132600</v>
       </c>
       <c r="E35" s="3">
-        <v>-270600</v>
+        <v>-226800</v>
       </c>
       <c r="F35" s="3">
-        <v>-200000</v>
+        <v>-184800</v>
       </c>
       <c r="G35" s="3">
-        <v>-76300</v>
+        <v>-67300</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>3</v>
@@ -1653,13 +1653,13 @@
         <v>79100</v>
       </c>
       <c r="E41" s="3">
-        <v>121300</v>
+        <v>124800</v>
       </c>
       <c r="F41" s="3">
-        <v>123800</v>
+        <v>152100</v>
       </c>
       <c r="G41" s="3">
-        <v>102900</v>
+        <v>111800</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>3</v>
@@ -1685,23 +1685,23 @@
       <c r="D42" s="3">
         <v>19400</v>
       </c>
-      <c r="E42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>3</v>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
+        <v>0</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -1716,16 +1716,16 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>291100</v>
+        <v>276500</v>
       </c>
       <c r="E43" s="3">
-        <v>484700</v>
+        <v>339900</v>
       </c>
       <c r="F43" s="3">
-        <v>159600</v>
+        <v>178200</v>
       </c>
       <c r="G43" s="3">
-        <v>151100</v>
+        <v>164200</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>3</v>
@@ -1752,13 +1752,13 @@
         <v>22700</v>
       </c>
       <c r="E44" s="3">
-        <v>44300</v>
+        <v>26500</v>
       </c>
       <c r="F44" s="3">
-        <v>31500</v>
+        <v>35200</v>
       </c>
       <c r="G44" s="3">
-        <v>33000</v>
+        <v>35800</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>3</v>
@@ -1782,16 +1782,16 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>51400</v>
+        <v>62300</v>
       </c>
       <c r="E45" s="3">
-        <v>96700</v>
+        <v>61600</v>
       </c>
       <c r="F45" s="3">
-        <v>31400</v>
+        <v>37800</v>
       </c>
       <c r="G45" s="3">
-        <v>55300</v>
+        <v>17400</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>3</v>
@@ -1815,16 +1815,16 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>463600</v>
+        <v>463800</v>
       </c>
       <c r="E46" s="3">
-        <v>543200</v>
+        <v>558700</v>
       </c>
       <c r="F46" s="3">
-        <v>346300</v>
+        <v>408000</v>
       </c>
       <c r="G46" s="3">
-        <v>342300</v>
+        <v>371900</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>3</v>
@@ -1851,10 +1851,10 @@
         <v>42400</v>
       </c>
       <c r="E47" s="3">
-        <v>49900</v>
+        <v>51300</v>
       </c>
       <c r="F47" s="3">
-        <v>190900</v>
+        <v>181400</v>
       </c>
       <c r="G47" s="3">
         <v>400</v>
@@ -1884,13 +1884,13 @@
         <v>34700</v>
       </c>
       <c r="E48" s="3">
-        <v>62500</v>
+        <v>34700</v>
       </c>
       <c r="F48" s="3">
-        <v>14500</v>
+        <v>17300</v>
       </c>
       <c r="G48" s="3">
-        <v>15000</v>
+        <v>16200</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>3</v>
@@ -1917,13 +1917,13 @@
         <v>25300</v>
       </c>
       <c r="E49" s="3">
-        <v>11500</v>
+        <v>6500</v>
       </c>
       <c r="F49" s="3">
-        <v>4400</v>
+        <v>4900</v>
       </c>
       <c r="G49" s="3">
-        <v>4200</v>
+        <v>4600</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>3</v>
@@ -2016,13 +2016,13 @@
         <v>35600</v>
       </c>
       <c r="E52" s="3">
-        <v>33800</v>
+        <v>34800</v>
       </c>
       <c r="F52" s="3">
-        <v>3100</v>
+        <v>3400</v>
       </c>
       <c r="G52" s="3">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>3</v>
@@ -2079,16 +2079,16 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>601700</v>
+        <v>601800</v>
       </c>
       <c r="E54" s="3">
-        <v>667000</v>
+        <v>685900</v>
       </c>
       <c r="F54" s="3">
-        <v>559200</v>
+        <v>615100</v>
       </c>
       <c r="G54" s="3">
-        <v>363500</v>
+        <v>394900</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>3</v>
@@ -2142,16 +2142,16 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>295600</v>
+        <v>297100</v>
       </c>
       <c r="E57" s="3">
-        <v>237800</v>
+        <v>269000</v>
       </c>
       <c r="F57" s="3">
-        <v>107400</v>
+        <v>139900</v>
       </c>
       <c r="G57" s="3">
-        <v>150500</v>
+        <v>205100</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>3</v>
@@ -2175,16 +2175,16 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>170600</v>
+        <v>174200</v>
       </c>
       <c r="E58" s="3">
-        <v>146400</v>
+        <v>130600</v>
       </c>
       <c r="F58" s="3">
-        <v>149300</v>
+        <v>146700</v>
       </c>
       <c r="G58" s="3">
-        <v>84300</v>
+        <v>49900</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>3</v>
@@ -2208,16 +2208,16 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>128100</v>
+        <v>72600</v>
       </c>
       <c r="E59" s="3">
-        <v>273600</v>
+        <v>119100</v>
       </c>
       <c r="F59" s="3">
-        <v>169400</v>
+        <v>104500</v>
       </c>
       <c r="G59" s="3">
-        <v>225900</v>
+        <v>220600</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>3</v>
@@ -2241,16 +2241,16 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>594300</v>
+        <v>594500</v>
       </c>
       <c r="E60" s="3">
-        <v>553700</v>
+        <v>569400</v>
       </c>
       <c r="F60" s="3">
-        <v>426100</v>
+        <v>433700</v>
       </c>
       <c r="G60" s="3">
-        <v>460700</v>
+        <v>500500</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>3</v>
@@ -2274,16 +2274,16 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>64200</v>
+        <v>79400</v>
       </c>
       <c r="E61" s="3">
-        <v>62000</v>
+        <v>73700</v>
       </c>
       <c r="F61" s="3">
         <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>109300</v>
+        <v>118800</v>
       </c>
       <c r="H61" s="3">
         <v>0</v>
@@ -2307,16 +2307,16 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>60800</v>
+        <v>26700</v>
       </c>
       <c r="E62" s="3">
-        <v>56100</v>
+        <v>6900</v>
       </c>
       <c r="F62" s="3">
-        <v>69000</v>
+        <v>2600</v>
       </c>
       <c r="G62" s="3">
-        <v>51700</v>
+        <v>1200</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>3</v>
@@ -2439,16 +2439,16 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>731600</v>
+        <v>719500</v>
       </c>
       <c r="E66" s="3">
-        <v>694700</v>
+        <v>690900</v>
       </c>
       <c r="F66" s="3">
-        <v>498600</v>
+        <v>510700</v>
       </c>
       <c r="G66" s="3">
-        <v>623300</v>
+        <v>675400</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>3</v>
@@ -2559,10 +2559,10 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>661500</v>
+        <v>713600</v>
       </c>
       <c r="G70" s="3">
-        <v>178300</v>
+        <v>35600</v>
       </c>
       <c r="H70" s="3">
         <v>0</v>
@@ -2619,16 +2619,16 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-940400</v>
+        <v>-940700</v>
       </c>
       <c r="E72" s="3">
-        <v>-807800</v>
+        <v>-830800</v>
       </c>
       <c r="F72" s="3">
-        <v>-601800</v>
+        <v>-645900</v>
       </c>
       <c r="G72" s="3">
-        <v>-461600</v>
+        <v>-343500</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>3</v>
@@ -2754,13 +2754,13 @@
         <v>-129900</v>
       </c>
       <c r="E76" s="3">
-        <v>-27700</v>
+        <v>-28500</v>
       </c>
       <c r="F76" s="3">
-        <v>-600900</v>
+        <v>-645000</v>
       </c>
       <c r="G76" s="3">
-        <v>-438100</v>
+        <v>-317900</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>3</v>
@@ -2855,16 +2855,16 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-132500</v>
+        <v>-132600</v>
       </c>
       <c r="E81" s="3">
-        <v>-270600</v>
+        <v>-226800</v>
       </c>
       <c r="F81" s="3">
-        <v>-200000</v>
+        <v>-184800</v>
       </c>
       <c r="G81" s="3">
-        <v>-76300</v>
+        <v>-67300</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>3</v>
@@ -2903,16 +2903,16 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>12100</v>
+        <v>7600</v>
       </c>
       <c r="E83" s="3">
-        <v>10500</v>
+        <v>7300</v>
       </c>
       <c r="F83" s="3">
-        <v>9200</v>
+        <v>6800</v>
       </c>
       <c r="G83" s="3">
-        <v>8300</v>
+        <v>5900</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>3</v>
@@ -3101,16 +3101,16 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-175300</v>
+        <v>-175400</v>
       </c>
       <c r="E89" s="3">
-        <v>-65000</v>
+        <v>-66900</v>
       </c>
       <c r="F89" s="3">
-        <v>-127900</v>
+        <v>-142800</v>
       </c>
       <c r="G89" s="3">
-        <v>-51900</v>
+        <v>-56400</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>3</v>
@@ -3152,13 +3152,13 @@
         <v>-8800</v>
       </c>
       <c r="E91" s="3">
-        <v>-22200</v>
+        <v>-22800</v>
       </c>
       <c r="F91" s="3">
-        <v>-12100</v>
+        <v>-13500</v>
       </c>
       <c r="G91" s="3">
-        <v>-9700</v>
+        <v>-10600</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>3</v>
@@ -3251,13 +3251,13 @@
         <v>83500</v>
       </c>
       <c r="E94" s="3">
-        <v>-44100</v>
+        <v>-45400</v>
       </c>
       <c r="F94" s="3">
-        <v>-168900</v>
+        <v>-188600</v>
       </c>
       <c r="G94" s="3">
-        <v>-12800</v>
+        <v>-14000</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>3</v>
@@ -3428,16 +3428,16 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>41800</v>
+        <v>41900</v>
       </c>
       <c r="E100" s="3">
-        <v>92700</v>
+        <v>95400</v>
       </c>
       <c r="F100" s="3">
-        <v>299300</v>
+        <v>334200</v>
       </c>
       <c r="G100" s="3">
-        <v>160500</v>
+        <v>174300</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>3</v>
@@ -3464,13 +3464,13 @@
         <v>5800</v>
       </c>
       <c r="E101" s="3">
-        <v>4100</v>
+        <v>4200</v>
       </c>
       <c r="F101" s="3">
-        <v>-4500</v>
+        <v>-5000</v>
       </c>
       <c r="G101" s="3">
-        <v>-1400</v>
+        <v>-1500</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>3</v>
@@ -3494,25 +3494,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-44100</v>
+        <v>-44200</v>
       </c>
       <c r="E102" s="3">
-        <v>-12400</v>
+        <v>-12700</v>
       </c>
       <c r="F102" s="3">
-        <v>-2100</v>
+        <v>-2300</v>
       </c>
       <c r="G102" s="3">
-        <v>94300</v>
-      </c>
-      <c r="H102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J102" s="3" t="s">
-        <v>3</v>
+        <v>102500</v>
+      </c>
+      <c r="H102" s="3">
+        <v>0</v>
+      </c>
+      <c r="I102" s="3">
+        <v>0</v>
+      </c>
+      <c r="J102" s="3">
+        <v>0</v>
       </c>
       <c r="K102" s="3" t="s">
         <v>3</v>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
   <si>
     <t>ECX</t>
   </si>
@@ -656,46 +656,46 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="12" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I7" s="2" t="s">
         <v>3</v>
       </c>
@@ -708,27 +708,30 @@
       <c r="L7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M7" s="2"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>761900</v>
+      </c>
+      <c r="E8" s="3">
         <v>658000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>516400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>437500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>343300</v>
       </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I8" s="3" t="s">
         <v>3</v>
       </c>
@@ -738,30 +741,33 @@
       <c r="K8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L8" s="3">
-        <v>0</v>
-      </c>
-      <c r="M8" s="3"/>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M8" s="3">
+        <v>0</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>603800</v>
+      </c>
+      <c r="E9" s="3">
         <v>478900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>372300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>308800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>258800</v>
       </c>
-      <c r="H9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I9" s="3" t="s">
         <v>3</v>
       </c>
@@ -774,27 +780,30 @@
       <c r="L9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>158100</v>
+      </c>
+      <c r="E10" s="3">
         <v>179100</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>144100</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>128600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>84500</v>
       </c>
-      <c r="H10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I10" s="3" t="s">
         <v>3</v>
       </c>
@@ -807,9 +816,12 @@
       <c r="L10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M10" s="3"/>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -823,26 +835,27 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>172600</v>
+      </c>
+      <c r="E12" s="3">
         <v>174000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>188700</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>190400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>108100</v>
       </c>
-      <c r="H12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I12" s="3" t="s">
         <v>3</v>
       </c>
@@ -855,9 +868,12 @@
       <c r="L12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M12" s="3"/>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -888,24 +904,27 @@
       <c r="L13" s="3">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="M13" s="3">
+        <v>0</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E14" s="3">
         <v>4600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-16700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-1700</v>
       </c>
-      <c r="G14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>3</v>
       </c>
@@ -918,45 +937,51 @@
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3"/>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="L14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E15" s="3">
         <v>12100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>7300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>5900</v>
       </c>
-      <c r="H15" s="3">
-        <v>0</v>
-      </c>
       <c r="I15" s="3">
         <v>0</v>
       </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
-      <c r="K15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="K15" s="3">
+        <v>0</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M15" s="3">
+        <v>0</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -967,26 +992,27 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>882800</v>
+      </c>
+      <c r="E17" s="3">
         <v>786000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>752500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>594900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>409200</v>
       </c>
-      <c r="H17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I17" s="3" t="s">
         <v>3</v>
       </c>
@@ -999,27 +1025,30 @@
       <c r="L17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M17" s="3"/>
-    </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-120900</v>
+      </c>
+      <c r="E18" s="3">
         <v>-128000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-236100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-157400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-65900</v>
       </c>
-      <c r="H18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1032,9 +1061,12 @@
       <c r="L18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M18" s="3"/>
-    </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1048,26 +1080,27 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
         <v>4200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3300</v>
       </c>
-      <c r="H20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1080,60 +1113,66 @@
       <c r="L20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M20" s="3"/>
-    </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-108400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-120100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-233700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-160400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-56800</v>
       </c>
-      <c r="H21" s="3">
-        <v>0</v>
-      </c>
       <c r="I21" s="3">
         <v>0</v>
       </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L21" s="3">
-        <v>0</v>
-      </c>
-      <c r="M21" s="3"/>
-    </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="K21" s="3">
+        <v>0</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M21" s="3">
+        <v>0</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E22" s="3">
         <v>11200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9100</v>
       </c>
-      <c r="H22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1143,30 +1182,33 @@
       <c r="K22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L22" s="3">
-        <v>0</v>
-      </c>
-      <c r="M22" s="3"/>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M22" s="3">
+        <v>0</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-135400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-143700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-228800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-184200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-67400</v>
       </c>
-      <c r="H23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1179,26 +1221,29 @@
       <c r="L23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M23" s="3"/>
-    </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>1100</v>
       </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>3</v>
+      <c r="H24" s="3">
+        <v>0</v>
       </c>
       <c r="I24" s="3" t="s">
         <v>3</v>
@@ -1209,12 +1254,15 @@
       <c r="K24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
-      <c r="M24" s="3"/>
-    </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1245,27 +1293,30 @@
       <c r="L25" s="3">
         <v>0</v>
       </c>
-      <c r="M25" s="3"/>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M25" s="3">
+        <v>0</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-135600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-143200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-233000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-185200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-67400</v>
       </c>
-      <c r="H26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1278,27 +1329,30 @@
       <c r="L26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M26" s="3"/>
-    </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-132600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-278200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-223300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-82900</v>
       </c>
-      <c r="H27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1311,9 +1365,12 @@
       <c r="L27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M27" s="3"/>
-    </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1344,9 +1401,12 @@
       <c r="L28" s="3">
         <v>0</v>
       </c>
-      <c r="M28" s="3"/>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M28" s="3">
+        <v>0</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1377,9 +1437,12 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3"/>
-    </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M29" s="3">
+        <v>0</v>
+      </c>
+      <c r="N29" s="3"/>
+    </row>
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1410,9 +1473,12 @@
       <c r="L30" s="3">
         <v>0</v>
       </c>
-      <c r="M30" s="3"/>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3"/>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1443,27 +1509,30 @@
       <c r="L31" s="3">
         <v>0</v>
       </c>
-      <c r="M31" s="3"/>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M31" s="3">
+        <v>0</v>
+      </c>
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3300</v>
       </c>
-      <c r="H32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1476,27 +1545,30 @@
       <c r="L32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M32" s="3"/>
-    </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-132600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-226800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-184800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-67300</v>
       </c>
-      <c r="H33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1509,9 +1581,12 @@
       <c r="L33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M33" s="3"/>
-    </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1542,27 +1617,30 @@
       <c r="L34" s="3">
         <v>0</v>
       </c>
-      <c r="M34" s="3"/>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M34" s="3">
+        <v>0</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-132600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-226800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-184800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-67300</v>
       </c>
-      <c r="H35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1575,32 +1653,35 @@
       <c r="L35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M35" s="3"/>
-    </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1613,9 +1694,12 @@
       <c r="L38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M38" s="2"/>
-    </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N38" s="2"/>
+    </row>
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1629,8 +1713,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1644,26 +1729,27 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E41" s="3">
         <v>79100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>124800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>152100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111800</v>
       </c>
-      <c r="H41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1676,18 +1762,21 @@
       <c r="L41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M41" s="3"/>
-    </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>17900</v>
+      </c>
+      <c r="E42" s="3">
         <v>19400</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
-      </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
@@ -1709,27 +1798,30 @@
       <c r="L42" s="3">
         <v>0</v>
       </c>
-      <c r="M42" s="3"/>
-    </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>225700</v>
+      </c>
+      <c r="E43" s="3">
         <v>276500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>339900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>178200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>164200</v>
       </c>
-      <c r="H43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1739,30 +1831,33 @@
       <c r="K43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
-      <c r="M43" s="3"/>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M43" s="3">
+        <v>0</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32000</v>
+      </c>
+      <c r="E44" s="3">
         <v>22700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>26500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>35200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35800</v>
       </c>
-      <c r="H44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1772,30 +1867,33 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
-      </c>
-      <c r="M44" s="3"/>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M44" s="3">
+        <v>0</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="3">
         <v>62300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>61600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>37800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17400</v>
       </c>
-      <c r="H45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1808,27 +1906,30 @@
       <c r="L45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M45" s="3"/>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N45" s="3"/>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>387900</v>
+      </c>
+      <c r="E46" s="3">
         <v>463800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>558700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>408000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>371900</v>
       </c>
-      <c r="H46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1841,27 +1942,30 @@
       <c r="L46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M46" s="3"/>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N46" s="3"/>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2200</v>
+      </c>
+      <c r="E47" s="3">
         <v>42400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>51300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>181400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>400</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1871,30 +1975,33 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
-      <c r="M47" s="3"/>
-    </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
+        <v>0</v>
+      </c>
+      <c r="N47" s="3"/>
+    </row>
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>34700</v>
+        <v>40100</v>
       </c>
       <c r="E48" s="3">
         <v>34700</v>
       </c>
       <c r="F48" s="3">
+        <v>34700</v>
+      </c>
+      <c r="G48" s="3">
         <v>17300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16200</v>
       </c>
-      <c r="H48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I48" s="3" t="s">
         <v>3</v>
       </c>
@@ -1904,30 +2011,33 @@
       <c r="K48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L48" s="3">
-        <v>0</v>
-      </c>
-      <c r="M48" s="3"/>
-    </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M48" s="3">
+        <v>0</v>
+      </c>
+      <c r="N48" s="3"/>
+    </row>
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E49" s="3">
         <v>25300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>6500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4600</v>
       </c>
-      <c r="H49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I49" s="3" t="s">
         <v>3</v>
       </c>
@@ -1937,12 +2047,15 @@
       <c r="K49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L49" s="3">
-        <v>0</v>
-      </c>
-      <c r="M49" s="3"/>
-    </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M49" s="3">
+        <v>0</v>
+      </c>
+      <c r="N49" s="3"/>
+    </row>
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -1973,9 +2086,12 @@
       <c r="L50" s="3">
         <v>0</v>
       </c>
-      <c r="M50" s="3"/>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M50" s="3">
+        <v>0</v>
+      </c>
+      <c r="N50" s="3"/>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2006,27 +2122,30 @@
       <c r="L51" s="3">
         <v>0</v>
       </c>
-      <c r="M51" s="3"/>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M51" s="3">
+        <v>0</v>
+      </c>
+      <c r="N51" s="3"/>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>40500</v>
+      </c>
+      <c r="E52" s="3">
         <v>35600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>34800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>3400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>1800</v>
       </c>
-      <c r="H52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2039,9 +2158,12 @@
       <c r="L52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M52" s="3"/>
-    </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N52" s="3"/>
+    </row>
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2072,27 +2194,30 @@
       <c r="L53" s="3">
         <v>0</v>
       </c>
-      <c r="M53" s="3"/>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M53" s="3">
+        <v>0</v>
+      </c>
+      <c r="N53" s="3"/>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>516700</v>
+      </c>
+      <c r="E54" s="3">
         <v>601800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>685900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>615100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>394900</v>
       </c>
-      <c r="H54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2105,9 +2230,12 @@
       <c r="L54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M54" s="3"/>
-    </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N54" s="3"/>
+    </row>
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2121,8 +2249,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2136,26 +2265,27 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>311300</v>
+      </c>
+      <c r="E57" s="3">
         <v>297100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>269000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>139900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>205100</v>
       </c>
-      <c r="H57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2165,30 +2295,33 @@
       <c r="K57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
-      <c r="M57" s="3"/>
-    </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M57" s="3">
+        <v>0</v>
+      </c>
+      <c r="N57" s="3"/>
+    </row>
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>256400</v>
+      </c>
+      <c r="E58" s="3">
         <v>174200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>130600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>146700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>49900</v>
       </c>
-      <c r="H58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2201,27 +2334,30 @@
       <c r="L58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M58" s="3"/>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N58" s="3"/>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48700</v>
+      </c>
+      <c r="E59" s="3">
         <v>72600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>119100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>104500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>220600</v>
       </c>
-      <c r="H59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2234,27 +2370,30 @@
       <c r="L59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M59" s="3"/>
-    </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N59" s="3"/>
+    </row>
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>702200</v>
+      </c>
+      <c r="E60" s="3">
         <v>594500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>569400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>433700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>500500</v>
       </c>
-      <c r="H60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2267,27 +2406,30 @@
       <c r="L60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M60" s="3"/>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N60" s="3"/>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>16600</v>
+      </c>
+      <c r="E61" s="3">
         <v>79400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>73700</v>
       </c>
-      <c r="F61" s="3">
-        <v>0</v>
-      </c>
       <c r="G61" s="3">
+        <v>0</v>
+      </c>
+      <c r="H61" s="3">
         <v>118800</v>
       </c>
-      <c r="H61" s="3">
-        <v>0</v>
-      </c>
       <c r="I61" s="3">
         <v>0</v>
       </c>
@@ -2300,27 +2442,30 @@
       <c r="L61" s="3">
         <v>0</v>
       </c>
-      <c r="M61" s="3"/>
-    </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M61" s="3">
+        <v>0</v>
+      </c>
+      <c r="N61" s="3"/>
+    </row>
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E62" s="3">
         <v>26700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>6900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1200</v>
       </c>
-      <c r="H62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2333,9 +2478,12 @@
       <c r="L62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M62" s="3"/>
-    </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N62" s="3"/>
+    </row>
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2366,9 +2514,12 @@
       <c r="L63" s="3">
         <v>0</v>
       </c>
-      <c r="M63" s="3"/>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M63" s="3">
+        <v>0</v>
+      </c>
+      <c r="N63" s="3"/>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2399,9 +2550,12 @@
       <c r="L64" s="3">
         <v>0</v>
       </c>
-      <c r="M64" s="3"/>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M64" s="3">
+        <v>0</v>
+      </c>
+      <c r="N64" s="3"/>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2432,27 +2586,30 @@
       <c r="L65" s="3">
         <v>0</v>
       </c>
-      <c r="M65" s="3"/>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M65" s="3">
+        <v>0</v>
+      </c>
+      <c r="N65" s="3"/>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>755700</v>
+      </c>
+      <c r="E66" s="3">
         <v>719500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>690900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>510700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>675400</v>
       </c>
-      <c r="H66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2465,9 +2622,12 @@
       <c r="L66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M66" s="3"/>
-    </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N66" s="3"/>
+    </row>
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2481,8 +2641,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2513,9 +2674,12 @@
       <c r="L68" s="3">
         <v>0</v>
       </c>
-      <c r="M68" s="3"/>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M68" s="3">
+        <v>0</v>
+      </c>
+      <c r="N68" s="3"/>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2546,9 +2710,12 @@
       <c r="L69" s="3">
         <v>0</v>
       </c>
-      <c r="M69" s="3"/>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M69" s="3">
+        <v>0</v>
+      </c>
+      <c r="N69" s="3"/>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2559,14 +2726,14 @@
         <v>0</v>
       </c>
       <c r="F70" s="3">
+        <v>0</v>
+      </c>
+      <c r="G70" s="3">
         <v>713600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>35600</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -2579,9 +2746,12 @@
       <c r="L70" s="3">
         <v>0</v>
       </c>
-      <c r="M70" s="3"/>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M70" s="3">
+        <v>0</v>
+      </c>
+      <c r="N70" s="3"/>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2612,27 +2782,30 @@
       <c r="L71" s="3">
         <v>0</v>
       </c>
-      <c r="M71" s="3"/>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M71" s="3">
+        <v>0</v>
+      </c>
+      <c r="N71" s="3"/>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1041600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-940700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-830800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-645900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-343500</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2645,9 +2818,12 @@
       <c r="L72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M72" s="3"/>
-    </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N72" s="3"/>
+    </row>
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2678,9 +2854,12 @@
       <c r="L73" s="3">
         <v>0</v>
       </c>
-      <c r="M73" s="3"/>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M73" s="3">
+        <v>0</v>
+      </c>
+      <c r="N73" s="3"/>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2711,9 +2890,12 @@
       <c r="L74" s="3">
         <v>0</v>
       </c>
-      <c r="M74" s="3"/>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M74" s="3">
+        <v>0</v>
+      </c>
+      <c r="N74" s="3"/>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2744,27 +2926,30 @@
       <c r="L75" s="3">
         <v>0</v>
       </c>
-      <c r="M75" s="3"/>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M75" s="3">
+        <v>0</v>
+      </c>
+      <c r="N75" s="3"/>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-241100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-129900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-28500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-645000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-317900</v>
       </c>
-      <c r="H76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2777,9 +2962,12 @@
       <c r="L76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M76" s="3"/>
-    </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N76" s="3"/>
+    </row>
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2810,32 +2998,35 @@
       <c r="L77" s="3">
         <v>0</v>
       </c>
-      <c r="M77" s="3"/>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="M77" s="3">
+        <v>0</v>
+      </c>
+      <c r="N77" s="3"/>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="I80" s="2" t="s">
         <v>3</v>
       </c>
@@ -2848,27 +3039,30 @@
       <c r="L80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="M80" s="2"/>
-    </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-127700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-132600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-226800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-184800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-67300</v>
       </c>
-      <c r="H81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I81" s="3" t="s">
         <v>3</v>
       </c>
@@ -2881,9 +3075,12 @@
       <c r="L81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M81" s="3"/>
-    </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N81" s="3"/>
+    </row>
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -2897,26 +3094,27 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
+      <c r="D83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E83" s="3">
         <v>7600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>6800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5900</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I83" s="3" t="s">
         <v>3</v>
       </c>
@@ -2926,12 +3124,15 @@
       <c r="K83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
-      <c r="M83" s="3"/>
-    </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M83" s="3">
+        <v>0</v>
+      </c>
+      <c r="N83" s="3"/>
+    </row>
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -2962,9 +3163,12 @@
       <c r="L84" s="3">
         <v>0</v>
       </c>
-      <c r="M84" s="3"/>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M84" s="3">
+        <v>0</v>
+      </c>
+      <c r="N84" s="3"/>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -2995,9 +3199,12 @@
       <c r="L85" s="3">
         <v>0</v>
       </c>
-      <c r="M85" s="3"/>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M85" s="3">
+        <v>0</v>
+      </c>
+      <c r="N85" s="3"/>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3028,9 +3235,12 @@
       <c r="L86" s="3">
         <v>0</v>
       </c>
-      <c r="M86" s="3"/>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M86" s="3">
+        <v>0</v>
+      </c>
+      <c r="N86" s="3"/>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3061,9 +3271,12 @@
       <c r="L87" s="3">
         <v>0</v>
       </c>
-      <c r="M87" s="3"/>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M87" s="3">
+        <v>0</v>
+      </c>
+      <c r="N87" s="3"/>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3094,27 +3307,30 @@
       <c r="L88" s="3">
         <v>0</v>
       </c>
-      <c r="M88" s="3"/>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M88" s="3">
+        <v>0</v>
+      </c>
+      <c r="N88" s="3"/>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3">
+      <c r="D89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E89" s="3">
         <v>-175400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-66900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-142800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-56400</v>
       </c>
-      <c r="H89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,9 +3343,12 @@
       <c r="L89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M89" s="3"/>
-    </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N89" s="3"/>
+    </row>
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3143,26 +3362,27 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
+      <c r="D91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-22800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-10600</v>
       </c>
-      <c r="H91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3172,12 +3392,15 @@
       <c r="K91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L91" s="3">
-        <v>0</v>
-      </c>
-      <c r="M91" s="3"/>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M91" s="3">
+        <v>0</v>
+      </c>
+      <c r="N91" s="3"/>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3208,9 +3431,12 @@
       <c r="L92" s="3">
         <v>0</v>
       </c>
-      <c r="M92" s="3"/>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M92" s="3">
+        <v>0</v>
+      </c>
+      <c r="N92" s="3"/>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3241,27 +3467,30 @@
       <c r="L93" s="3">
         <v>0</v>
       </c>
-      <c r="M93" s="3"/>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M93" s="3">
+        <v>0</v>
+      </c>
+      <c r="N93" s="3"/>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3">
+      <c r="D94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E94" s="3">
         <v>83500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-45400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-188600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-14000</v>
       </c>
-      <c r="H94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3274,9 +3503,12 @@
       <c r="L94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M94" s="3"/>
-    </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3290,8 +3522,9 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3322,9 +3555,12 @@
       <c r="L96" s="3">
         <v>0</v>
       </c>
-      <c r="M96" s="3"/>
-    </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M96" s="3">
+        <v>0</v>
+      </c>
+      <c r="N96" s="3"/>
+    </row>
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3355,9 +3591,12 @@
       <c r="L97" s="3">
         <v>0</v>
       </c>
-      <c r="M97" s="3"/>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M97" s="3">
+        <v>0</v>
+      </c>
+      <c r="N97" s="3"/>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3388,9 +3627,12 @@
       <c r="L98" s="3">
         <v>0</v>
       </c>
-      <c r="M98" s="3"/>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M98" s="3">
+        <v>0</v>
+      </c>
+      <c r="N98" s="3"/>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3421,27 +3663,30 @@
       <c r="L99" s="3">
         <v>0</v>
       </c>
-      <c r="M99" s="3"/>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M99" s="3">
+        <v>0</v>
+      </c>
+      <c r="N99" s="3"/>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3">
+      <c r="D100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E100" s="3">
         <v>41900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>95400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>334200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>174300</v>
       </c>
-      <c r="H100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3454,27 +3699,30 @@
       <c r="L100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M100" s="3"/>
-    </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="M100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N100" s="3"/>
+    </row>
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
+      <c r="D101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E101" s="3">
         <v>5800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1500</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3484,43 +3732,49 @@
       <c r="K101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
-      <c r="M101" s="3"/>
-    </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="L101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3"/>
+    </row>
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3">
         <v>-44200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>102500</v>
       </c>
-      <c r="H102" s="3">
-        <v>0</v>
-      </c>
       <c r="I102" s="3">
         <v>0</v>
       </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
-      <c r="K102" s="3" t="s">
-        <v>3</v>
+      <c r="K102" s="3">
+        <v>0</v>
       </c>
       <c r="L102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M102" s="3"/>
+      <c r="M102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="92">
   <si>
     <t>ECX</t>
   </si>
@@ -721,7 +721,7 @@
         <v>761900</v>
       </c>
       <c r="E8" s="3">
-        <v>658000</v>
+        <v>662800</v>
       </c>
       <c r="F8" s="3">
         <v>516400</v>
@@ -757,7 +757,7 @@
         <v>603800</v>
       </c>
       <c r="E9" s="3">
-        <v>478900</v>
+        <v>483300</v>
       </c>
       <c r="F9" s="3">
         <v>372300</v>
@@ -793,7 +793,7 @@
         <v>158100</v>
       </c>
       <c r="E10" s="3">
-        <v>179100</v>
+        <v>179500</v>
       </c>
       <c r="F10" s="3">
         <v>144100</v>
@@ -842,7 +842,7 @@
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>172600</v>
+        <v>169200</v>
       </c>
       <c r="E12" s="3">
         <v>174000</v>
@@ -913,8 +913,8 @@
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
+      <c r="D14" s="3">
+        <v>6300</v>
       </c>
       <c r="E14" s="3">
         <v>4600</v>
@@ -950,13 +950,13 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>11800</v>
+        <v>20300</v>
       </c>
       <c r="E15" s="3">
         <v>12100</v>
       </c>
       <c r="F15" s="3">
-        <v>7300</v>
+        <v>10800</v>
       </c>
       <c r="G15" s="3">
         <v>6800</v>
@@ -999,10 +999,10 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>882800</v>
+        <v>882500</v>
       </c>
       <c r="E17" s="3">
-        <v>786000</v>
+        <v>790800</v>
       </c>
       <c r="F17" s="3">
         <v>752500</v>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-120900</v>
+        <v>-120600</v>
       </c>
       <c r="E18" s="3">
         <v>-128000</v>
@@ -1087,10 +1087,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-700</v>
+        <v>-6800</v>
       </c>
       <c r="E20" s="3">
-        <v>4200</v>
+        <v>4300</v>
       </c>
       <c r="F20" s="3">
         <v>4900</v>
@@ -1123,13 +1123,13 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-108400</v>
+        <v>-93600</v>
       </c>
       <c r="E21" s="3">
         <v>-120100</v>
       </c>
       <c r="F21" s="3">
-        <v>-233700</v>
+        <v>-230200</v>
       </c>
       <c r="G21" s="3">
         <v>-160400</v>
@@ -1519,10 +1519,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>700</v>
+        <v>6800</v>
       </c>
       <c r="E32" s="3">
-        <v>-4200</v>
+        <v>-4300</v>
       </c>
       <c r="F32" s="3">
         <v>-4900</v>
@@ -1739,7 +1739,7 @@
         <v>44400</v>
       </c>
       <c r="E41" s="3">
-        <v>79100</v>
+        <v>80600</v>
       </c>
       <c r="F41" s="3">
         <v>124800</v>
@@ -1808,10 +1808,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>225700</v>
+        <v>243500</v>
       </c>
       <c r="E43" s="3">
-        <v>276500</v>
+        <v>280300</v>
       </c>
       <c r="F43" s="3">
         <v>339900</v>
@@ -1844,7 +1844,7 @@
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>32000</v>
+        <v>32100</v>
       </c>
       <c r="E44" s="3">
         <v>22700</v>
@@ -1879,11 +1879,11 @@
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3" t="s">
-        <v>3</v>
+      <c r="D45" s="3">
+        <v>44200</v>
       </c>
       <c r="E45" s="3">
-        <v>62300</v>
+        <v>62500</v>
       </c>
       <c r="F45" s="3">
         <v>61600</v>
@@ -1919,7 +1919,7 @@
         <v>387900</v>
       </c>
       <c r="E46" s="3">
-        <v>463800</v>
+        <v>469400</v>
       </c>
       <c r="F46" s="3">
         <v>558700</v>
@@ -2207,7 +2207,7 @@
         <v>516700</v>
       </c>
       <c r="E54" s="3">
-        <v>601800</v>
+        <v>607400</v>
       </c>
       <c r="F54" s="3">
         <v>685900</v>
@@ -2275,7 +2275,7 @@
         <v>311300</v>
       </c>
       <c r="E57" s="3">
-        <v>297100</v>
+        <v>302300</v>
       </c>
       <c r="F57" s="3">
         <v>269000</v>
@@ -2344,7 +2344,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>48700</v>
+        <v>99300</v>
       </c>
       <c r="E59" s="3">
         <v>72600</v>
@@ -2383,7 +2383,7 @@
         <v>702200</v>
       </c>
       <c r="E60" s="3">
-        <v>594500</v>
+        <v>599700</v>
       </c>
       <c r="F60" s="3">
         <v>569400</v>
@@ -2599,7 +2599,7 @@
         <v>755700</v>
       </c>
       <c r="E66" s="3">
-        <v>719500</v>
+        <v>724700</v>
       </c>
       <c r="F66" s="3">
         <v>690900</v>
@@ -2939,7 +2939,7 @@
         <v>-241100</v>
       </c>
       <c r="E76" s="3">
-        <v>-129900</v>
+        <v>-129500</v>
       </c>
       <c r="F76" s="3">
         <v>-28500</v>
@@ -3100,8 +3100,8 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>3</v>
+      <c r="D83" s="3">
+        <v>7800</v>
       </c>
       <c r="E83" s="3">
         <v>7600</v>
@@ -3316,11 +3316,11 @@
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="D89" s="3" t="s">
-        <v>3</v>
+      <c r="D89" s="3">
+        <v>-58900</v>
       </c>
       <c r="E89" s="3">
-        <v>-175400</v>
+        <v>-173900</v>
       </c>
       <c r="F89" s="3">
         <v>-66900</v>
@@ -3368,8 +3368,8 @@
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3" t="s">
-        <v>3</v>
+      <c r="D91" s="3">
+        <v>-15700</v>
       </c>
       <c r="E91" s="3">
         <v>-8800</v>
@@ -3476,8 +3476,8 @@
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D94" s="3" t="s">
-        <v>3</v>
+      <c r="D94" s="3">
+        <v>-8200</v>
       </c>
       <c r="E94" s="3">
         <v>83500</v>
@@ -3672,8 +3672,8 @@
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="D100" s="3" t="s">
-        <v>3</v>
+      <c r="D100" s="3">
+        <v>35800</v>
       </c>
       <c r="E100" s="3">
         <v>41900</v>
@@ -3708,11 +3708,11 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3" t="s">
-        <v>3</v>
+      <c r="D101" s="3">
+        <v>-400</v>
       </c>
       <c r="E101" s="3">
-        <v>5800</v>
+        <v>5900</v>
       </c>
       <c r="F101" s="3">
         <v>4200</v>
@@ -3745,10 +3745,10 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>0</v>
+        <v>-31700</v>
       </c>
       <c r="E102" s="3">
-        <v>-44200</v>
+        <v>-42700</v>
       </c>
       <c r="F102" s="3">
         <v>-12700</v>

--- a/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ECX_YR_FIN.xlsx
@@ -656,49 +656,49 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:O102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="13" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="14" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J7" s="2" t="s">
         <v>3</v>
       </c>
@@ -711,30 +711,33 @@
       <c r="M7" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>761900</v>
+        <v>847900</v>
       </c>
       <c r="E8" s="3">
-        <v>662800</v>
+        <v>771500</v>
       </c>
       <c r="F8" s="3">
+        <v>662200</v>
+      </c>
+      <c r="G8" s="3">
         <v>516400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>437500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>343300</v>
       </c>
-      <c r="I8" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J8" s="3" t="s">
         <v>3</v>
       </c>
@@ -744,33 +747,36 @@
       <c r="L8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M8" s="3">
-        <v>0</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="3">
+        <v>0</v>
+      </c>
+      <c r="O8" s="3"/>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
-        <v>603800</v>
+        <v>686600</v>
       </c>
       <c r="E9" s="3">
-        <v>483300</v>
+        <v>611400</v>
       </c>
       <c r="F9" s="3">
+        <v>483600</v>
+      </c>
+      <c r="G9" s="3">
         <v>372300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>308800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>258800</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J9" s="3" t="s">
         <v>3</v>
       </c>
@@ -783,30 +789,33 @@
       <c r="M9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O9" s="3"/>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
-        <v>158100</v>
+        <v>161300</v>
       </c>
       <c r="E10" s="3">
-        <v>179500</v>
+        <v>160100</v>
       </c>
       <c r="F10" s="3">
+        <v>178600</v>
+      </c>
+      <c r="G10" s="3">
         <v>144100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>128600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>84500</v>
       </c>
-      <c r="I10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J10" s="3" t="s">
         <v>3</v>
       </c>
@@ -819,9 +828,12 @@
       <c r="M10" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O10" s="3"/>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -836,29 +848,30 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
-        <v>169200</v>
+        <v>117100</v>
       </c>
       <c r="E12" s="3">
-        <v>174000</v>
+        <v>171500</v>
       </c>
       <c r="F12" s="3">
+        <v>173000</v>
+      </c>
+      <c r="G12" s="3">
         <v>188700</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>190400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>108100</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J12" s="3" t="s">
         <v>3</v>
       </c>
@@ -871,9 +884,12 @@
       <c r="M12" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O12" s="3"/>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -907,27 +923,30 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3"/>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E14" s="3">
         <v>6300</v>
       </c>
-      <c r="E14" s="3">
-        <v>4600</v>
-      </c>
       <c r="F14" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G14" s="3">
         <v>-16700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-1700</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I14" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,48 +959,54 @@
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="M14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3"/>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>20300</v>
+        <v>19900</v>
       </c>
       <c r="E15" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F15" s="3">
         <v>12100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>5900</v>
       </c>
-      <c r="I15" s="3">
-        <v>0</v>
-      </c>
       <c r="J15" s="3">
         <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="L15" s="3">
+        <v>0</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="3">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -993,29 +1018,30 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+    </row>
+    <row r="17" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>882500</v>
+        <v>899000</v>
       </c>
       <c r="E17" s="3">
-        <v>790800</v>
+        <v>894200</v>
       </c>
       <c r="F17" s="3">
+        <v>790400</v>
+      </c>
+      <c r="G17" s="3">
         <v>752500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>594900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>409200</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J17" s="3" t="s">
         <v>3</v>
       </c>
@@ -1028,30 +1054,33 @@
       <c r="M17" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O17" s="3"/>
+    </row>
+    <row r="18" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-120600</v>
+        <v>-51100</v>
       </c>
       <c r="E18" s="3">
-        <v>-128000</v>
+        <v>-122700</v>
       </c>
       <c r="F18" s="3">
+        <v>-128200</v>
+      </c>
+      <c r="G18" s="3">
         <v>-236100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-157400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-65900</v>
       </c>
-      <c r="I18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1064,9 +1093,12 @@
       <c r="M18" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O18" s="3"/>
+    </row>
+    <row r="19" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1081,29 +1113,30 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+    </row>
+    <row r="20" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-6800</v>
+        <v>-7400</v>
       </c>
       <c r="E20" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="F20" s="3">
         <v>4300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9800</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3300</v>
       </c>
-      <c r="I20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1116,66 +1149,72 @@
       <c r="M20" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O20" s="3"/>
+    </row>
+    <row r="21" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-93600</v>
+        <v>-23900</v>
       </c>
       <c r="E21" s="3">
-        <v>-120100</v>
+        <v>-95100</v>
       </c>
       <c r="F21" s="3">
+        <v>-120400</v>
+      </c>
+      <c r="G21" s="3">
         <v>-230200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-160400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-56800</v>
       </c>
-      <c r="I21" s="3">
-        <v>0</v>
-      </c>
       <c r="J21" s="3">
         <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>0</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M21" s="3">
-        <v>0</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="L21" s="3">
+        <v>0</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N21" s="3">
+        <v>0</v>
+      </c>
+      <c r="O21" s="3"/>
+    </row>
+    <row r="22" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>18300</v>
+        <v>23800</v>
       </c>
       <c r="E22" s="3">
+        <v>18600</v>
+      </c>
+      <c r="F22" s="3">
         <v>11200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9100</v>
       </c>
-      <c r="I22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1185,33 +1224,36 @@
       <c r="L22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+      <c r="O22" s="3"/>
+    </row>
+    <row r="23" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>-135400</v>
+        <v>-67700</v>
       </c>
       <c r="E23" s="3">
-        <v>-143700</v>
+        <v>-137500</v>
       </c>
       <c r="F23" s="3">
+        <v>-144400</v>
+      </c>
+      <c r="G23" s="3">
         <v>-228800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-184200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-67400</v>
       </c>
-      <c r="I23" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J23" s="3" t="s">
         <v>3</v>
       </c>
@@ -1224,29 +1266,32 @@
       <c r="M23" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O23" s="3"/>
+    </row>
+    <row r="24" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1100</v>
       </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>3</v>
+      <c r="I24" s="3">
+        <v>0</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>3</v>
@@ -1257,12 +1302,15 @@
       <c r="L24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3"/>
+    </row>
+    <row r="25" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1296,30 +1344,33 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3"/>
+    </row>
+    <row r="26" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>-135600</v>
+        <v>-68900</v>
       </c>
       <c r="E26" s="3">
-        <v>-143200</v>
+        <v>-137800</v>
       </c>
       <c r="F26" s="3">
+        <v>-143900</v>
+      </c>
+      <c r="G26" s="3">
         <v>-233000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-185200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-67400</v>
       </c>
-      <c r="I26" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J26" s="3" t="s">
         <v>3</v>
       </c>
@@ -1332,30 +1383,33 @@
       <c r="M26" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O26" s="3"/>
+    </row>
+    <row r="27" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>-127700</v>
+        <v>-66000</v>
       </c>
       <c r="E27" s="3">
-        <v>-132600</v>
+        <v>-129800</v>
       </c>
       <c r="F27" s="3">
+        <v>-133300</v>
+      </c>
+      <c r="G27" s="3">
         <v>-278200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-223300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-82900</v>
       </c>
-      <c r="I27" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J27" s="3" t="s">
         <v>3</v>
       </c>
@@ -1368,9 +1422,12 @@
       <c r="M27" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O27" s="3"/>
+    </row>
+    <row r="28" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1404,9 +1461,12 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3"/>
+    </row>
+    <row r="29" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1440,9 +1500,12 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+    </row>
+    <row r="30" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1476,9 +1539,12 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3"/>
+    </row>
+    <row r="31" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1512,30 +1578,33 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3"/>
+    </row>
+    <row r="32" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>6800</v>
+        <v>7400</v>
       </c>
       <c r="E32" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-4300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9800</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3300</v>
       </c>
-      <c r="I32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J32" s="3" t="s">
         <v>3</v>
       </c>
@@ -1548,30 +1617,33 @@
       <c r="M32" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O32" s="3"/>
+    </row>
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-127700</v>
+        <v>-66000</v>
       </c>
       <c r="E33" s="3">
-        <v>-132600</v>
+        <v>-129800</v>
       </c>
       <c r="F33" s="3">
+        <v>-133300</v>
+      </c>
+      <c r="G33" s="3">
         <v>-226800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-184800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-67300</v>
       </c>
-      <c r="I33" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J33" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,9 +1656,12 @@
       <c r="M33" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O33" s="3"/>
+    </row>
+    <row r="34" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1620,30 +1695,33 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+    </row>
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-127700</v>
+        <v>-66000</v>
       </c>
       <c r="E35" s="3">
-        <v>-132600</v>
+        <v>-129800</v>
       </c>
       <c r="F35" s="3">
+        <v>-133300</v>
+      </c>
+      <c r="G35" s="3">
         <v>-226800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-184800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-67300</v>
       </c>
-      <c r="I35" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J35" s="3" t="s">
         <v>3</v>
       </c>
@@ -1656,35 +1734,38 @@
       <c r="M35" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O35" s="3"/>
+    </row>
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J38" s="2" t="s">
         <v>3</v>
       </c>
@@ -1697,9 +1778,12 @@
       <c r="M38" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1714,8 +1798,9 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+    </row>
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1730,29 +1815,30 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+    </row>
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>44400</v>
+        <v>87100</v>
       </c>
       <c r="E41" s="3">
+        <v>44300</v>
+      </c>
+      <c r="F41" s="3">
         <v>80600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>124800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>152100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111800</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>3</v>
       </c>
@@ -1765,21 +1851,24 @@
       <c r="M41" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O41" s="3"/>
+    </row>
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E42" s="3">
         <v>17900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>19400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -1801,30 +1890,33 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3"/>
+    </row>
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>243500</v>
+        <v>260000</v>
       </c>
       <c r="E43" s="3">
+        <v>242600</v>
+      </c>
+      <c r="F43" s="3">
         <v>280300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>339900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>178200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>164200</v>
       </c>
-      <c r="I43" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J43" s="3" t="s">
         <v>3</v>
       </c>
@@ -1834,33 +1926,36 @@
       <c r="L43" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3"/>
+    </row>
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>32100</v>
+        <v>62300</v>
       </c>
       <c r="E44" s="3">
+        <v>31900</v>
+      </c>
+      <c r="F44" s="3">
         <v>22700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>26500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>35200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>35800</v>
       </c>
-      <c r="I44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
@@ -1870,33 +1965,36 @@
       <c r="L44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+      <c r="O44" s="3"/>
+    </row>
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>44200</v>
+        <v>36400</v>
       </c>
       <c r="E45" s="3">
+        <v>43600</v>
+      </c>
+      <c r="F45" s="3">
         <v>62500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>61600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>37800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17400</v>
       </c>
-      <c r="I45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J45" s="3" t="s">
         <v>3</v>
       </c>
@@ -1909,30 +2007,33 @@
       <c r="M45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O45" s="3"/>
+    </row>
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>387900</v>
+        <v>483200</v>
       </c>
       <c r="E46" s="3">
+        <v>386100</v>
+      </c>
+      <c r="F46" s="3">
         <v>469400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>558700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>408000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>371900</v>
       </c>
-      <c r="I46" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J46" s="3" t="s">
         <v>3</v>
       </c>
@@ -1945,30 +2046,33 @@
       <c r="M46" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O46" s="3"/>
+    </row>
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>61500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>42400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>51300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>181400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>400</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -1978,33 +2082,36 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
+        <v>0</v>
+      </c>
+      <c r="O47" s="3"/>
+    </row>
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E48" s="3">
         <v>40100</v>
-      </c>
-      <c r="E48" s="3">
-        <v>34700</v>
       </c>
       <c r="F48" s="3">
         <v>34700</v>
       </c>
       <c r="G48" s="3">
+        <v>34700</v>
+      </c>
+      <c r="H48" s="3">
         <v>17300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16200</v>
       </c>
-      <c r="I48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J48" s="3" t="s">
         <v>3</v>
       </c>
@@ -2014,33 +2121,36 @@
       <c r="L48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M48" s="3">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N48" s="3">
+        <v>0</v>
+      </c>
+      <c r="O48" s="3"/>
+    </row>
+    <row r="49" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>46000</v>
+        <v>44100</v>
       </c>
       <c r="E49" s="3">
+        <v>45700</v>
+      </c>
+      <c r="F49" s="3">
         <v>25300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>6500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>4900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>4600</v>
       </c>
-      <c r="I49" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J49" s="3" t="s">
         <v>3</v>
       </c>
@@ -2050,12 +2160,15 @@
       <c r="L49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M49" s="3">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3"/>
+    </row>
+    <row r="50" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2089,9 +2202,12 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3"/>
+    </row>
+    <row r="51" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2125,30 +2241,33 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3"/>
+    </row>
+    <row r="52" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>40500</v>
+        <v>30200</v>
       </c>
       <c r="E52" s="3">
+        <v>40300</v>
+      </c>
+      <c r="F52" s="3">
         <v>35600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>34800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>3400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>1800</v>
       </c>
-      <c r="I52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J52" s="3" t="s">
         <v>3</v>
       </c>
@@ -2161,9 +2280,12 @@
       <c r="M52" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O52" s="3"/>
+    </row>
+    <row r="53" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2197,30 +2319,33 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3"/>
+    </row>
+    <row r="54" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>516700</v>
+        <v>662400</v>
       </c>
       <c r="E54" s="3">
+        <v>514300</v>
+      </c>
+      <c r="F54" s="3">
         <v>607400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>685900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>615100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>394900</v>
       </c>
-      <c r="I54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J54" s="3" t="s">
         <v>3</v>
       </c>
@@ -2233,9 +2358,12 @@
       <c r="M54" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O54" s="3"/>
+    </row>
+    <row r="55" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2250,8 +2378,9 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+    </row>
+    <row r="56" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2266,29 +2395,30 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+    </row>
+    <row r="57" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>311300</v>
+        <v>316600</v>
       </c>
       <c r="E57" s="3">
+        <v>309600</v>
+      </c>
+      <c r="F57" s="3">
         <v>302300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>269000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>139900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>205100</v>
       </c>
-      <c r="I57" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J57" s="3" t="s">
         <v>3</v>
       </c>
@@ -2298,33 +2428,36 @@
       <c r="L57" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M57" s="3">
-        <v>0</v>
-      </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N57" s="3">
+        <v>0</v>
+      </c>
+      <c r="O57" s="3"/>
+    </row>
+    <row r="58" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>256400</v>
+        <v>383200</v>
       </c>
       <c r="E58" s="3">
+        <v>277700</v>
+      </c>
+      <c r="F58" s="3">
         <v>174200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>130600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>146700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>49900</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J58" s="3" t="s">
         <v>3</v>
       </c>
@@ -2337,30 +2470,33 @@
       <c r="M58" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O58" s="3"/>
+    </row>
+    <row r="59" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>99300</v>
+        <v>76300</v>
       </c>
       <c r="E59" s="3">
+        <v>74700</v>
+      </c>
+      <c r="F59" s="3">
         <v>72600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>119100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>104500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>220600</v>
       </c>
-      <c r="I59" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J59" s="3" t="s">
         <v>3</v>
       </c>
@@ -2373,30 +2509,33 @@
       <c r="M59" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O59" s="3"/>
+    </row>
+    <row r="60" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>702200</v>
+        <v>823000</v>
       </c>
       <c r="E60" s="3">
+        <v>698700</v>
+      </c>
+      <c r="F60" s="3">
         <v>599700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>569400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>433700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>500500</v>
       </c>
-      <c r="I60" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J60" s="3" t="s">
         <v>3</v>
       </c>
@@ -2409,30 +2548,33 @@
       <c r="M60" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O60" s="3"/>
+    </row>
+    <row r="61" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>16600</v>
+        <v>81600</v>
       </c>
       <c r="E61" s="3">
+        <v>16700</v>
+      </c>
+      <c r="F61" s="3">
         <v>79400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>73700</v>
       </c>
-      <c r="G61" s="3">
-        <v>0</v>
-      </c>
       <c r="H61" s="3">
+        <v>0</v>
+      </c>
+      <c r="I61" s="3">
         <v>118800</v>
       </c>
-      <c r="I61" s="3">
-        <v>0</v>
-      </c>
       <c r="J61" s="3">
         <v>0</v>
       </c>
@@ -2445,30 +2587,33 @@
       <c r="M61" s="3">
         <v>0</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3"/>
+    </row>
+    <row r="62" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>29700</v>
+        <v>18900</v>
       </c>
       <c r="E62" s="3">
-        <v>26700</v>
+        <v>16200</v>
       </c>
       <c r="F62" s="3">
+        <v>19800</v>
+      </c>
+      <c r="G62" s="3">
         <v>6900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2600</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1200</v>
       </c>
-      <c r="I62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J62" s="3" t="s">
         <v>3</v>
       </c>
@@ -2481,9 +2626,12 @@
       <c r="M62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O62" s="3"/>
+    </row>
+    <row r="63" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2517,9 +2665,12 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3"/>
+    </row>
+    <row r="64" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2553,9 +2704,12 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3"/>
+    </row>
+    <row r="65" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2589,30 +2743,33 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3"/>
+    </row>
+    <row r="66" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>755700</v>
+        <v>945900</v>
       </c>
       <c r="E66" s="3">
+        <v>752000</v>
+      </c>
+      <c r="F66" s="3">
         <v>724700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>690900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>510700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>675400</v>
       </c>
-      <c r="I66" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J66" s="3" t="s">
         <v>3</v>
       </c>
@@ -2625,9 +2782,12 @@
       <c r="M66" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O66" s="3"/>
+    </row>
+    <row r="67" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2642,8 +2802,9 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+    </row>
+    <row r="68" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2677,9 +2838,12 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3"/>
+    </row>
+    <row r="69" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2713,9 +2877,12 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3"/>
+    </row>
+    <row r="70" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2729,14 +2896,14 @@
         <v>0</v>
       </c>
       <c r="G70" s="3">
+        <v>0</v>
+      </c>
+      <c r="H70" s="3">
         <v>713600</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>35600</v>
       </c>
-      <c r="I70" s="3">
-        <v>0</v>
-      </c>
       <c r="J70" s="3">
         <v>0</v>
       </c>
@@ -2749,9 +2916,12 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+      <c r="O70" s="3"/>
+    </row>
+    <row r="71" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2785,30 +2955,33 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3"/>
+    </row>
+    <row r="72" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>-1041600</v>
+        <v>-1190500</v>
       </c>
       <c r="E72" s="3">
+        <v>-1124500</v>
+      </c>
+      <c r="F72" s="3">
         <v>-940700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-830800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-645900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-343500</v>
       </c>
-      <c r="I72" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J72" s="3" t="s">
         <v>3</v>
       </c>
@@ -2821,9 +2994,12 @@
       <c r="M72" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O72" s="3"/>
+    </row>
+    <row r="73" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2857,9 +3033,12 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3"/>
+    </row>
+    <row r="74" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2893,9 +3072,12 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3"/>
+    </row>
+    <row r="75" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2929,30 +3111,33 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3"/>
+    </row>
+    <row r="76" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>-241100</v>
+        <v>-282700</v>
       </c>
       <c r="E76" s="3">
+        <v>-239700</v>
+      </c>
+      <c r="F76" s="3">
         <v>-129500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-28500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-645000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-317900</v>
       </c>
-      <c r="I76" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J76" s="3" t="s">
         <v>3</v>
       </c>
@@ -2965,9 +3150,12 @@
       <c r="M76" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O76" s="3"/>
+    </row>
+    <row r="77" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3001,35 +3189,38 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3"/>
+    </row>
+    <row r="79" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:15" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="J80" s="2" t="s">
         <v>3</v>
       </c>
@@ -3042,30 +3233,33 @@
       <c r="M80" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-127700</v>
+        <v>-66000</v>
       </c>
       <c r="E81" s="3">
-        <v>-132600</v>
+        <v>-129800</v>
       </c>
       <c r="F81" s="3">
+        <v>-133300</v>
+      </c>
+      <c r="G81" s="3">
         <v>-226800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-184800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-67300</v>
       </c>
-      <c r="I81" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J81" s="3" t="s">
         <v>3</v>
       </c>
@@ -3078,9 +3272,12 @@
       <c r="M81" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O81" s="3"/>
+    </row>
+    <row r="82" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3095,29 +3292,30 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+    </row>
+    <row r="83" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>7800</v>
+        <v>7700</v>
       </c>
       <c r="E83" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F83" s="3">
         <v>7600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5900</v>
       </c>
-      <c r="I83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J83" s="3" t="s">
         <v>3</v>
       </c>
@@ -3127,12 +3325,15 @@
       <c r="L83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
-      </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N83" s="3">
+        <v>0</v>
+      </c>
+      <c r="O83" s="3"/>
+    </row>
+    <row r="84" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3166,9 +3367,12 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3"/>
+    </row>
+    <row r="85" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3202,9 +3406,12 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3"/>
+    </row>
+    <row r="86" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3238,9 +3445,12 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3"/>
+    </row>
+    <row r="87" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3274,9 +3484,12 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3"/>
+    </row>
+    <row r="88" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3310,30 +3523,33 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3"/>
+    </row>
+    <row r="89" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-58900</v>
+        <v>-94400</v>
       </c>
       <c r="E89" s="3">
-        <v>-173900</v>
+        <v>-60000</v>
       </c>
       <c r="F89" s="3">
+        <v>-172400</v>
+      </c>
+      <c r="G89" s="3">
         <v>-66900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-142800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-56400</v>
       </c>
-      <c r="I89" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J89" s="3" t="s">
         <v>3</v>
       </c>
@@ -3346,9 +3562,12 @@
       <c r="M89" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O89" s="3"/>
+    </row>
+    <row r="90" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3363,29 +3582,30 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+    </row>
+    <row r="91" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-15700</v>
+        <v>-12200</v>
       </c>
       <c r="E91" s="3">
-        <v>-8800</v>
+        <v>-15900</v>
       </c>
       <c r="F91" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="G91" s="3">
         <v>-22800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-10600</v>
       </c>
-      <c r="I91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J91" s="3" t="s">
         <v>3</v>
       </c>
@@ -3395,12 +3615,15 @@
       <c r="L91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M91" s="3">
-        <v>0</v>
-      </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+      <c r="O91" s="3"/>
+    </row>
+    <row r="92" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3434,9 +3657,12 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3"/>
+    </row>
+    <row r="93" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3470,30 +3696,33 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3"/>
+    </row>
+    <row r="94" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-8200</v>
+        <v>-70500</v>
       </c>
       <c r="E94" s="3">
-        <v>83500</v>
+        <v>-8100</v>
       </c>
       <c r="F94" s="3">
+        <v>87300</v>
+      </c>
+      <c r="G94" s="3">
         <v>-45400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-188600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-14000</v>
       </c>
-      <c r="I94" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J94" s="3" t="s">
         <v>3</v>
       </c>
@@ -3506,9 +3735,12 @@
       <c r="M94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O94" s="3"/>
+    </row>
+    <row r="95" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3523,8 +3755,9 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+    </row>
+    <row r="96" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -3558,9 +3791,12 @@
       <c r="M96" s="3">
         <v>0</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N96" s="3">
+        <v>0</v>
+      </c>
+      <c r="O96" s="3"/>
+    </row>
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3594,9 +3830,12 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3"/>
+    </row>
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3630,9 +3869,12 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3"/>
+    </row>
+    <row r="99" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3666,30 +3908,33 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3"/>
+    </row>
+    <row r="100" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>35800</v>
+        <v>203900</v>
       </c>
       <c r="E100" s="3">
-        <v>41900</v>
+        <v>36400</v>
       </c>
       <c r="F100" s="3">
+        <v>40600</v>
+      </c>
+      <c r="G100" s="3">
         <v>95400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>334200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>174300</v>
       </c>
-      <c r="I100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J100" s="3" t="s">
         <v>3</v>
       </c>
@@ -3702,30 +3947,33 @@
       <c r="M100" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O100" s="3"/>
+    </row>
+    <row r="101" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-400</v>
+        <v>4100</v>
       </c>
       <c r="E101" s="3">
-        <v>5900</v>
+        <v>-2200</v>
       </c>
       <c r="F101" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="G101" s="3">
         <v>4200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1500</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
       </c>
@@ -3735,46 +3983,52 @@
       <c r="L101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-31700</v>
+        <v>43100</v>
       </c>
       <c r="E102" s="3">
-        <v>-42700</v>
+        <v>-33900</v>
       </c>
       <c r="F102" s="3">
+        <v>-46600</v>
+      </c>
+      <c r="G102" s="3">
         <v>-12700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>102500</v>
       </c>
-      <c r="I102" s="3">
-        <v>0</v>
-      </c>
       <c r="J102" s="3">
         <v>0</v>
       </c>
       <c r="K102" s="3">
         <v>0</v>
       </c>
-      <c r="L102" s="3" t="s">
-        <v>3</v>
+      <c r="L102" s="3">
+        <v>0</v>
       </c>
       <c r="M102" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="N102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="O102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
